--- a/datos/crudo/bess_desempleo.xlsx
+++ b/datos/crudo/bess_desempleo.xlsx
@@ -5,11 +5,11 @@
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" hidePivotFieldList="1" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\Area Seguimiento y Monitoreo de Estadisticas\BESS\BESS 2026\JUNIO 2026\VALORES\DISEÑO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\Area Seguimiento y Monitoreo de Estadisticas\BESS\BESS 2026\SEPTIEMBRE 2026\VALORES\DISEÑO\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9735" tabRatio="839"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="839"/>
   </bookViews>
   <sheets>
     <sheet name="Indice" sheetId="9" r:id="rId1"/>
@@ -20,12 +20,22 @@
     <sheet name="5.4" sheetId="111" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'5.1'!$A$1:$F$69</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'5.1'!$A$1:$F$72</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'5.2'!$A$1:$F$34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'5.3'!$A$1:$K$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'5.4'!$A$1:$E$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'5.4'!$A$1:$E$34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Indice!$A$1:$A$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'INTRO PD'!$A$1:$F$4</definedName>
+    <definedName name="FemaleDa">#N/A</definedName>
+    <definedName name="Input_File">#N/A</definedName>
+    <definedName name="MaleData">#N/A</definedName>
+    <definedName name="Maximum">#N/A</definedName>
+    <definedName name="Maximum_used">#N/A</definedName>
+    <definedName name="Pyramid_Filename">#N/A</definedName>
+    <definedName name="Pyramid_Title">#N/A</definedName>
+    <definedName name="Stop_at_age">#N/A</definedName>
+    <definedName name="Test">#N/A</definedName>
+    <definedName name="TITL">#N/A</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
@@ -208,18 +218,6 @@
     <t>Consideraciones metodológicas</t>
   </si>
   <si>
-    <t>La Ley N° 24.013 establece el Sistema Integral de Prestaciones por Desempleo. 
-La protección instituida por esta ley alcanza a los trabajadores cuyo contrato de trabajo se rige por la Ley de Contrato de Trabajo N° 20.744  (t.o. 1976) y a los trabajadores comprendidos en el Régimen Nacional de la Industria de la Construcción (Ley N° 25.371) que hayan aportado al Fondo Nacional de Empleo (FNE).
-Para tener derecho a las prestaciones se debe estar en situación legal de desempleo, haber cotizado al FNE por un periodo mínimo de 6 meses durante los 3 años previos al cese del contrato de trabajo,   90 días en los últimos 12 meses si se trata de servicios eventuales y no percibir beneficios previsionales ni prestaciones no contributivas.
-Hay dos elementos que caracterizan las prestaciones por desempleo: la duración y la cuantía.
-La duración del beneficio, desde 2 hasta 12 meses, depende de la cantidad de meses trabajados con anterioridad a la situación legal de desempleo. En el caso de trabajadores eventuales será de un día por cada 3 días trabajados con cotización siempre que la contratación sea superior a 30 días. 
-El monto es un porcentaje del importe neto de la mejor remuneración normal y habitual de los 6 meses previos al desempleo. El Consejo Nacional del empleo, la productividad y el salario mínimo vital y móvil establece el monto mínimo y máximo de la prestación.
-La prestación es decreciente, los primeros 4 meses corresponde el 100% del beneficio, del quinto al octavo el 80% y del noveno al duodécimo, el 70% del monto inicialmente determinado.
-Ser beneficiario de la prestación por desempleo da derecho a prestaciones médico asistenciales de acuerdo con las Leyes N° 23.660 y 23.661, a las asignaciones familiares que correspondieren y al reconocimiento del periodo de prestaciones por desempleo a los efectos previsionales. 
-En este capítulo se presenta la serie cronológica de altas anuales y beneficiarios, junto con la prestación promedio con y sin asignaciones familiares.
-Los beneficiarios se informan, también, desagregados por sexo, grupos de edad y rama de actividad económica.</t>
-  </si>
-  <si>
     <t>2020</t>
   </si>
   <si>
@@ -399,35 +397,6 @@
     <t>(2) El valor de las altas anuales corresponde al total del año 2026 mientras que la cantidad de beneficiarios es la del mes pertinente.</t>
   </si>
   <si>
-    <t>5.2 Beneficiarios de la prestación por desempleo según sexo y grupos de edad. Junio 2026</t>
-  </si>
-  <si>
-    <t>5.4 Beneficiarios de la prestación por desempleo según sexo y jurisdicción. Junio 2026</t>
-  </si>
-  <si>
-    <t>CUADRO 5.2 BENEFICIARIOS DE LA PRESTACIÓN POR DESEMPLEO SEGÚN SEXO Y GRUPOS DE EDAD. JUNIO 2026</t>
-  </si>
-  <si>
-    <t>BENEFICIARIOS DE LA PRESTACIÓN POR DESEMPLEO SEGÚN SEXO Y GRUPOS DE EDAD. JUNIO 2026</t>
-  </si>
-  <si>
-    <t>CUADRO 5.4 BENEFICIARIOS DE LA PRESTACIÓN POR DESEMPLEO SEGÚN SEXO Y JURISDICCIÓN. JUNIO 2026</t>
-  </si>
-  <si>
-    <r>
-      <t>90.634</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(2)</t>
-    </r>
-  </si>
-  <si>
     <r>
       <t>2026</t>
     </r>
@@ -479,14 +448,54 @@
     <t>(3)  Sin Clasificar: CLAE informada erróneamente.</t>
   </si>
   <si>
-    <t>(1) Datos hasta junio de 2026.</t>
+    <t>La Ley N° 24.013 establece el Sistema Integral de Prestaciones por Desempleo. 
+La protección instituida por esta ley alcanza a los trabajadores cuyo contrato de trabajo se rige por la Ley de Contrato de Trabajo N° 20.744  (t.o. 1976), a los trabajadores y trabajadoras del Régimen Especial de Contrato de Trabajo para el Personal de Casas Particulares comprendidos en la Ley N° 26.844, a los trabajadores comprendidos en el Régimen Nacional de la Industria de la Construcción (Ley N° 25.371) que hayan aportado al Fondo Nacional de Empleo (FNE).
+Para tener derecho a las prestaciones se debe estar en situación legal de desempleo, haber cotizado al FNE por un periodo mínimo exigido en la normativa correspondiente.
+Hay dos elementos que caracterizan las prestaciones por desempleo: la duración y la cuantía.
+El monto es un porcentaje del importe neto de la mejor remuneración normal y habitual de los 6 meses previos al desempleo. El Consejo Nacional del empleo, la productividad y el salario mínimo vital y móvil establece el monto mínimo y máximo de la prestación.
+La prestación es decreciente, los primeros 4 meses corresponde el 100% del beneficio, del quinto al octavo el 80% y del noveno al duodécimo, el 70% del monto inicialmente determinado.
+Ser beneficiario de la prestación por desempleo da derecho a prestaciones médico asistenciales de acuerdo con las Leyes N° 23.660 y 23.661, a las asignaciones familiares que correspondieren y al reconocimiento del periodo de prestaciones por desempleo a los efectos previsionales. 
+En este capítulo se presenta la serie cronológica de altas anuales y beneficiarios, junto con la prestación promedio con y sin asignaciones familiares.
+Los beneficiarios se informan, también, desagregados por sexo, grupos de edad y rama de actividad económica.</t>
+  </si>
+  <si>
+    <t>CUADRO 5.2 BENEFICIARIOS DE LA PRESTACIÓN POR DESEMPLEO SEGÚN SEXO Y GRUPOS DE EDAD. SEPTIEMBRE 2026</t>
+  </si>
+  <si>
+    <t>BENEFICIARIOS DE LA PRESTACIÓN POR DESEMPLEO SEGÚN SEXO Y GRUPOS DE EDAD. SEPTIEMBRE 2026</t>
+  </si>
+  <si>
+    <t>CUADRO 5.4 BENEFICIARIOS DE LA PRESTACIÓN POR DESEMPLEO SEGÚN SEXO Y JURISDICCIÓN. SEPTIEMBRE 2026</t>
+  </si>
+  <si>
+    <r>
+      <t>145.004</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(2)</t>
+    </r>
+  </si>
+  <si>
+    <t>5.2 Beneficiarios de la prestación por desempleo según sexo y grupos de edad. Septiembre 2026</t>
+  </si>
+  <si>
+    <t>5.4 Beneficiarios de la prestación por desempleo según sexo y jurisdicción. Septiembre 2026</t>
+  </si>
+  <si>
+    <t>(1) Datos hasta septiembre de 2026.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="7">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="#,##0_ ;\-#,##0\ "/>
@@ -494,11 +503,20 @@
     <numFmt numFmtId="168" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="169" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="170" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * #,##0_ ;_ @_ "/>
+    <numFmt numFmtId="171" formatCode="General_)"/>
+    <numFmt numFmtId="172" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="54" x14ac:knownFonts="1">
+  <fonts count="57" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -812,12 +830,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <i/>
       <sz val="10"/>
       <color theme="1"/>
@@ -831,6 +843,10 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Courier"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -841,6 +857,21 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="30">
@@ -1666,544 +1697,558 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="75">
+  <cellStyleXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="36" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="36" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="37" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="36" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="36" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="37" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="51" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="52" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="51" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="36" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="36" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="35" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="38" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="39" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="justify" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="38" fillId="25" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="39" fillId="25" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="39" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="32" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="32" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="31" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="43" fillId="27" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="31" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="44" fillId="27" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="48" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="49" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="46" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="47" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="46" fillId="25" borderId="0" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="46" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="68" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="47" fillId="25" borderId="0" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="47" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="68" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="68"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="68" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="68"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="68" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="68" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="68" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="50" fillId="0" borderId="0" xfId="68" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="45" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="45" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="49" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="40" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="40" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="49" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="40" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="40" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="47" fillId="25" borderId="0" xfId="68" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="31" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="31" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="31" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="31" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="31" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="31" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="0" xfId="31" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" xfId="31" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="170" fontId="39" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="40" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="39" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="40" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="39" fillId="25" borderId="12" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="8" fillId="25" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="40" fillId="25" borderId="12" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="9" fillId="25" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="25" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="25" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="8" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="9" fillId="25" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="39" fillId="0" borderId="42" xfId="68" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="40" fillId="0" borderId="42" xfId="68" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="39" fillId="0" borderId="43" xfId="68" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="40" fillId="0" borderId="43" xfId="68" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="30" fillId="0" borderId="44" xfId="68" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="44" xfId="68" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="30" fillId="0" borderId="46" xfId="68" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="46" xfId="68" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="30" fillId="0" borderId="48" xfId="68" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="48" xfId="68" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="30" fillId="0" borderId="47" xfId="68" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="47" xfId="68" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="16" xfId="68" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="16" xfId="68" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="17" xfId="68" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" xfId="68" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="23" xfId="68" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="23" xfId="68" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="41" xfId="68" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="41" xfId="68" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="24" borderId="33" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="24" borderId="33" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="30" fillId="24" borderId="33" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="31" fillId="24" borderId="33" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="24" borderId="14" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="24" borderId="14" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="30" fillId="24" borderId="14" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="31" fillId="24" borderId="14" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="25" borderId="14" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="25" borderId="14" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="30" fillId="25" borderId="14" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="31" fillId="25" borderId="14" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="25" borderId="0" xfId="68" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" xfId="68" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" xfId="68" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" xfId="68" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" xfId="68" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="46" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" xfId="68" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="47" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="25" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="9" fillId="25" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="47" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="74" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="17" fontId="8" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="17" fontId="9" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="25" borderId="51" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="25" borderId="51" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="25" borderId="50" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="25" borderId="50" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="74" applyFont="1"/>
-    <xf numFmtId="169" fontId="46" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="47" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="17" fontId="8" fillId="24" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="17" fontId="9" fillId="24" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="25" borderId="24" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="25" borderId="24" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="25" borderId="9" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="25" borderId="9" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="30" fillId="25" borderId="28" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="31" fillId="25" borderId="28" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="52" fillId="24" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="74" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="24" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="25" borderId="32" xfId="68" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="25" borderId="32" xfId="68" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="53" fillId="25" borderId="32" xfId="68" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="54" fillId="25" borderId="32" xfId="68" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="52" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="53" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="52" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="53" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="0" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="68" applyFont="1"/>
+    <xf numFmtId="0" fontId="48" fillId="25" borderId="0" xfId="68" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="56" fillId="25" borderId="0" xfId="68" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="48" fillId="0" borderId="0" xfId="68" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="justify" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="26" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="26" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="26" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="26" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="24" borderId="54" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="24" borderId="24" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="24" borderId="53" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="24" borderId="54" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="24" borderId="24" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="24" borderId="53" xfId="33" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="39" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="40" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="39" fillId="25" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="40" fillId="25" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="39" fillId="25" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="40" fillId="25" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="39" fillId="25" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="40" fillId="25" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="0" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="21" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="21" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="27" borderId="0" xfId="69" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="55" fillId="27" borderId="0" xfId="69" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="75">
+  <cellStyles count="78">
     <cellStyle name="20% - Énfasis1" xfId="1" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Énfasis2" xfId="2" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Énfasis3" xfId="3" builtinId="38" customBuiltin="1"/>
@@ -2244,6 +2289,7 @@
     <cellStyle name="Hipervínculo 2" xfId="69"/>
     <cellStyle name="Incorrecto" xfId="32" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Millares" xfId="33" builtinId="3"/>
+    <cellStyle name="Millares 11" xfId="77"/>
     <cellStyle name="Millares 2" xfId="47"/>
     <cellStyle name="Millares 2 2" xfId="61"/>
     <cellStyle name="Millares 2 3" xfId="59"/>
@@ -2259,12 +2305,14 @@
     <cellStyle name="Normal 2 2" xfId="37"/>
     <cellStyle name="Normal 2 2 2" xfId="53"/>
     <cellStyle name="Normal 2 3" xfId="48"/>
+    <cellStyle name="Normal 2 4" xfId="75"/>
     <cellStyle name="Normal 3" xfId="46"/>
     <cellStyle name="Normal 3 2" xfId="60"/>
     <cellStyle name="Normal 3 3" xfId="58"/>
     <cellStyle name="Normal 4" xfId="62"/>
     <cellStyle name="Normal 5" xfId="65"/>
     <cellStyle name="Normal 6" xfId="68"/>
+    <cellStyle name="Normal 6 2" xfId="76"/>
     <cellStyle name="Normal 7" xfId="70"/>
     <cellStyle name="Normal 8" xfId="71"/>
     <cellStyle name="Notas" xfId="38" builtinId="10" customBuiltin="1"/>
@@ -2352,10 +2400,10 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>'5.1'!$E$6:$E$36</c:f>
+              <c:f>'5.1'!$E$6:$E$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>2001</c:v>
                 </c:pt>
@@ -2449,15 +2497,24 @@
                 <c:pt idx="30" formatCode="mmm\-yy">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="31" formatCode="mmm\-yy">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="32" formatCode="mmm\-yy">
+                  <c:v>46235</c:v>
+                </c:pt>
+                <c:pt idx="33" formatCode="mmm\-yy">
+                  <c:v>46266</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'5.1'!$C$6:$C$36</c:f>
+              <c:f>'5.1'!$C$6:$C$39</c:f>
               <c:numCache>
                 <c:formatCode>_ * #,##0_ ;_ * \-#,##0_ ;_ * "-"??_ ;_ @_ </c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>143041</c:v>
                 </c:pt>
@@ -2551,6 +2608,15 @@
                 <c:pt idx="30">
                   <c:v>116641</c:v>
                 </c:pt>
+                <c:pt idx="31">
+                  <c:v>117451</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>123648</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>127613</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2570,11 +2636,11 @@
         </c:dLbls>
         <c:gapWidth val="25"/>
         <c:overlap val="100"/>
-        <c:axId val="361869664"/>
-        <c:axId val="365176432"/>
+        <c:axId val="-627384528"/>
+        <c:axId val="-627383440"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="361869664"/>
+        <c:axId val="-627384528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2645,7 +2711,7 @@
             <a:endParaRPr lang="es-AR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="365176432"/>
+        <c:crossAx val="-627383440"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2653,9 +2719,10 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="365176432"/>
+        <c:axId val="-627383440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="200000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2740,7 +2807,7 @@
             <a:endParaRPr lang="es-AR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="361869664"/>
+        <c:crossAx val="-627384528"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2892,34 +2959,34 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>-109</c:v>
+                  <c:v>-116</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-4053</c:v>
+                  <c:v>-4291</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-8484</c:v>
+                  <c:v>-8991</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-10286</c:v>
+                  <c:v>-11269</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-10542</c:v>
+                  <c:v>-11369</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-9841</c:v>
+                  <c:v>-10647</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-13574</c:v>
+                  <c:v>-14949</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-10492</c:v>
+                  <c:v>-11576</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-7102</c:v>
+                  <c:v>-7933</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-4562</c:v>
+                  <c:v>-5147</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3001,34 +3068,34 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>38</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2060</c:v>
+                  <c:v>2129</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4782</c:v>
+                  <c:v>5372</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5601</c:v>
+                  <c:v>6168</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5647</c:v>
+                  <c:v>6189</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4928</c:v>
+                  <c:v>5511</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6460</c:v>
+                  <c:v>7133</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4802</c:v>
+                  <c:v>5266</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2990</c:v>
+                  <c:v>3229</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>288</c:v>
+                  <c:v>301</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3049,11 +3116,11 @@
         </c:dLbls>
         <c:gapWidth val="25"/>
         <c:overlap val="100"/>
-        <c:axId val="365054560"/>
-        <c:axId val="365053776"/>
+        <c:axId val="-627381808"/>
+        <c:axId val="-627381264"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="365054560"/>
+        <c:axId val="-627381808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3123,7 +3190,7 @@
             <a:endParaRPr lang="es-AR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="365053776"/>
+        <c:crossAx val="-627381264"/>
         <c:crossesAt val="0"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3132,7 +3199,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="365053776"/>
+        <c:axId val="-627381264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3215,7 +3282,7 @@
             <a:endParaRPr lang="es-AR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="365054560"/>
+        <c:crossAx val="-627381808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3313,13 +3380,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>45720</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>68580</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3742,102 +3809,102 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="108.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="132.28515625" style="99" customWidth="1"/>
-    <col min="2" max="16384" width="108.85546875" style="99"/>
+    <col min="1" max="1" width="132.28515625" style="100" customWidth="1"/>
+    <col min="2" max="16384" width="108.85546875" style="100"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="96" t="s">
+    <row r="1" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="97" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="98"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="99"/>
     </row>
     <row r="2" spans="1:5" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="100"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="97"/>
-    </row>
-    <row r="3" spans="1:5" s="103" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="101" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="102"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
+      <c r="A2" s="101"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="98"/>
+    </row>
+    <row r="3" spans="1:5" s="104" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="102" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
     </row>
     <row r="4" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="101" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="104"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="104"/>
+      <c r="B4" s="105"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
     </row>
     <row r="5" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="105"/>
-      <c r="B5" s="104"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
+      <c r="A5" s="106"/>
+      <c r="B5" s="105"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
     </row>
     <row r="6" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="100" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6" s="106"/>
-      <c r="C6" s="98"/>
-      <c r="D6" s="106"/>
+      <c r="A6" s="101" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="107"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="107"/>
     </row>
     <row r="7" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="100" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="106"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="104"/>
+      <c r="A7" s="101" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="107"/>
+      <c r="C7" s="99"/>
+      <c r="D7" s="105"/>
     </row>
     <row r="8" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="100" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="106"/>
-      <c r="C8" s="98"/>
-      <c r="D8" s="106"/>
+      <c r="A8" s="101" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="107"/>
+      <c r="C8" s="99"/>
+      <c r="D8" s="107"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="100" t="s">
-        <v>88</v>
-      </c>
-      <c r="B9" s="106"/>
-      <c r="C9" s="98"/>
-      <c r="D9" s="106"/>
+      <c r="A9" s="101" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="107"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="107"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="107"/>
-      <c r="B10" s="98"/>
-      <c r="C10" s="98"/>
-      <c r="D10" s="98"/>
+      <c r="A10" s="108"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="98"/>
-      <c r="B11" s="98"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
+      <c r="A11" s="99"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="162"/>
-      <c r="B12" s="162"/>
-      <c r="C12" s="162"/>
-      <c r="D12" s="162"/>
+      <c r="A12" s="167"/>
+      <c r="B12" s="167"/>
+      <c r="C12" s="167"/>
+      <c r="D12" s="167"/>
       <c r="E12" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A12:D12"/>
   </mergeCells>
-  <phoneticPr fontId="44" type="noConversion"/>
+  <phoneticPr fontId="45" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A6:C6" location="'4.1'!A1" display="3.1 Beneficiarios, prestación promedio y altas anuales del Sistema Integral de Prestaciones por Desempleo. 2001 - 2019"/>
     <hyperlink ref="A7" location="'5.2'!Área_de_impresión" display="5.2 Beneficiarios de la prestación por desempleo según sexo y grupos de edad. Marzo 2022"/>
@@ -3879,16 +3946,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="165" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="166"/>
-      <c r="C1" s="164" t="s">
+      <c r="A1" s="170" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="171"/>
+      <c r="C1" s="169" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
       <c r="G1" s="71" t="s">
         <v>18</v>
       </c>
@@ -3897,14 +3964,14 @@
       <c r="C2" s="28"/>
     </row>
     <row r="3" spans="1:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="163" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="163"/>
-      <c r="C3" s="163"/>
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
+      <c r="A3" s="168" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="168"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
+      <c r="E3" s="168"/>
+      <c r="F3" s="168"/>
     </row>
     <row r="4" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="27"/>
@@ -3920,7 +3987,7 @@
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <phoneticPr fontId="44" type="noConversion"/>
+  <phoneticPr fontId="45" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G1" location="Indice!A1" display="volver al índice"/>
   </hyperlinks>
@@ -3944,24 +4011,24 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O262"/>
+  <dimension ref="A1:O265"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.140625" style="13" customWidth="1"/>
-    <col min="2" max="4" width="17.140625" style="12" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="13" customWidth="1"/>
-    <col min="6" max="6" width="6" style="13" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" style="13" customWidth="1"/>
+    <col min="2" max="4" width="17.7109375" style="12" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="13" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" style="13" customWidth="1"/>
     <col min="7" max="39" width="10.28515625" style="13" customWidth="1"/>
     <col min="40" max="16384" width="12.42578125" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="170" t="s">
-        <v>83</v>
-      </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
+      <c r="A1" s="175" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
       <c r="E1" s="71" t="s">
         <v>18</v>
       </c>
@@ -3974,16 +4041,16 @@
       <c r="D3" s="39"/>
     </row>
     <row r="4" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="173" t="s">
+      <c r="A4" s="178" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="171" t="s">
+      <c r="B4" s="176" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="171" t="s">
+      <c r="C4" s="176" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="171" t="s">
+      <c r="D4" s="176" t="s">
         <v>44</v>
       </c>
       <c r="E4" s="11"/>
@@ -3999,10 +4066,10 @@
       <c r="O4" s="11"/>
     </row>
     <row r="5" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="174"/>
-      <c r="B5" s="172"/>
-      <c r="C5" s="172"/>
-      <c r="D5" s="172"/>
+      <c r="A5" s="179"/>
+      <c r="B5" s="177"/>
+      <c r="C5" s="177"/>
+      <c r="D5" s="177"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
@@ -4019,19 +4086,19 @@
       <c r="A6" s="64">
         <v>2001</v>
       </c>
-      <c r="B6" s="127">
+      <c r="B6" s="128">
         <v>240950</v>
       </c>
-      <c r="C6" s="128">
+      <c r="C6" s="129">
         <v>143041</v>
       </c>
-      <c r="D6" s="128">
+      <c r="D6" s="129">
         <v>204</v>
       </c>
-      <c r="E6" s="156">
+      <c r="E6" s="158">
         <v>2001</v>
       </c>
-      <c r="F6" s="147"/>
+      <c r="F6" s="148"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
@@ -4046,19 +4113,19 @@
       <c r="A7" s="65">
         <v>2002</v>
       </c>
-      <c r="B7" s="129">
+      <c r="B7" s="130">
         <v>259066</v>
       </c>
-      <c r="C7" s="130">
+      <c r="C7" s="131">
         <v>197799</v>
       </c>
-      <c r="D7" s="130">
+      <c r="D7" s="131">
         <v>197</v>
       </c>
-      <c r="E7" s="156">
+      <c r="E7" s="158">
         <v>2002</v>
       </c>
-      <c r="F7" s="147"/>
+      <c r="F7" s="148"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
@@ -4073,19 +4140,19 @@
       <c r="A8" s="65">
         <v>2003</v>
       </c>
-      <c r="B8" s="129">
+      <c r="B8" s="130">
         <v>110150</v>
       </c>
-      <c r="C8" s="130">
+      <c r="C8" s="131">
         <v>98307</v>
       </c>
-      <c r="D8" s="130">
+      <c r="D8" s="131">
         <v>200</v>
       </c>
-      <c r="E8" s="156">
+      <c r="E8" s="158">
         <v>2003</v>
       </c>
-      <c r="F8" s="147"/>
+      <c r="F8" s="148"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
@@ -4100,19 +4167,19 @@
       <c r="A9" s="65">
         <v>2004</v>
       </c>
-      <c r="B9" s="129">
+      <c r="B9" s="130">
         <v>90525</v>
       </c>
-      <c r="C9" s="130">
+      <c r="C9" s="131">
         <v>60101</v>
       </c>
-      <c r="D9" s="130">
+      <c r="D9" s="131">
         <v>219</v>
       </c>
-      <c r="E9" s="156">
+      <c r="E9" s="158">
         <v>2004</v>
       </c>
-      <c r="F9" s="147"/>
+      <c r="F9" s="148"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
@@ -4127,19 +4194,19 @@
       <c r="A10" s="65">
         <v>2005</v>
       </c>
-      <c r="B10" s="129">
+      <c r="B10" s="130">
         <v>107310</v>
       </c>
-      <c r="C10" s="130">
+      <c r="C10" s="131">
         <v>62508</v>
       </c>
-      <c r="D10" s="130">
+      <c r="D10" s="131">
         <v>242</v>
       </c>
-      <c r="E10" s="156">
+      <c r="E10" s="158">
         <v>2005</v>
       </c>
-      <c r="F10" s="147"/>
+      <c r="F10" s="148"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -4154,19 +4221,19 @@
       <c r="A11" s="65">
         <v>2006</v>
       </c>
-      <c r="B11" s="129">
+      <c r="B11" s="130">
         <v>143606</v>
       </c>
-      <c r="C11" s="130">
+      <c r="C11" s="131">
         <v>79092</v>
       </c>
-      <c r="D11" s="130">
+      <c r="D11" s="131">
         <v>319</v>
       </c>
-      <c r="E11" s="156">
+      <c r="E11" s="158">
         <v>2006</v>
       </c>
-      <c r="F11" s="147"/>
+      <c r="F11" s="148"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
@@ -4181,19 +4248,19 @@
       <c r="A12" s="65">
         <v>2007</v>
       </c>
-      <c r="B12" s="129">
+      <c r="B12" s="130">
         <v>162257</v>
       </c>
-      <c r="C12" s="130">
+      <c r="C12" s="131">
         <v>93284</v>
       </c>
-      <c r="D12" s="130">
+      <c r="D12" s="131">
         <v>344</v>
       </c>
-      <c r="E12" s="156">
+      <c r="E12" s="158">
         <v>2007</v>
       </c>
-      <c r="F12" s="147"/>
+      <c r="F12" s="148"/>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
@@ -4208,19 +4275,19 @@
       <c r="A13" s="65">
         <v>2008</v>
       </c>
-      <c r="B13" s="129">
+      <c r="B13" s="130">
         <v>200684</v>
       </c>
-      <c r="C13" s="130">
+      <c r="C13" s="131">
         <v>109748</v>
       </c>
-      <c r="D13" s="130">
+      <c r="D13" s="131">
         <v>352</v>
       </c>
-      <c r="E13" s="156">
+      <c r="E13" s="158">
         <v>2008</v>
       </c>
-      <c r="F13" s="147"/>
+      <c r="F13" s="148"/>
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
@@ -4235,16 +4302,16 @@
       <c r="A14" s="65">
         <v>2009</v>
       </c>
-      <c r="B14" s="129">
+      <c r="B14" s="130">
         <v>243487</v>
       </c>
-      <c r="C14" s="130">
+      <c r="C14" s="131">
         <v>142928</v>
       </c>
-      <c r="D14" s="130">
+      <c r="D14" s="131">
         <v>356</v>
       </c>
-      <c r="E14" s="156">
+      <c r="E14" s="158">
         <v>2009</v>
       </c>
       <c r="F14" s="37"/>
@@ -4253,16 +4320,16 @@
       <c r="A15" s="65">
         <v>2010</v>
       </c>
-      <c r="B15" s="129">
+      <c r="B15" s="130">
         <v>193237</v>
       </c>
-      <c r="C15" s="130">
+      <c r="C15" s="131">
         <v>127386</v>
       </c>
-      <c r="D15" s="130">
+      <c r="D15" s="131">
         <v>351</v>
       </c>
-      <c r="E15" s="156">
+      <c r="E15" s="158">
         <v>2010</v>
       </c>
       <c r="F15" s="37"/>
@@ -4271,16 +4338,16 @@
       <c r="A16" s="65">
         <v>2011</v>
       </c>
-      <c r="B16" s="129">
+      <c r="B16" s="130">
         <v>161549</v>
       </c>
-      <c r="C16" s="130">
+      <c r="C16" s="131">
         <v>103602</v>
       </c>
-      <c r="D16" s="130">
+      <c r="D16" s="131">
         <v>354</v>
       </c>
-      <c r="E16" s="156">
+      <c r="E16" s="158">
         <v>2011</v>
       </c>
       <c r="F16" s="37"/>
@@ -4289,16 +4356,16 @@
       <c r="A17" s="65">
         <v>2012</v>
       </c>
-      <c r="B17" s="129">
+      <c r="B17" s="130">
         <v>165323</v>
       </c>
-      <c r="C17" s="130">
+      <c r="C17" s="131">
         <v>99219</v>
       </c>
-      <c r="D17" s="130">
+      <c r="D17" s="131">
         <v>357</v>
       </c>
-      <c r="E17" s="156">
+      <c r="E17" s="158">
         <v>2012</v>
       </c>
       <c r="F17" s="37"/>
@@ -4307,16 +4374,16 @@
       <c r="A18" s="65">
         <v>2013</v>
       </c>
-      <c r="B18" s="129">
+      <c r="B18" s="130">
         <v>139925</v>
       </c>
-      <c r="C18" s="130">
+      <c r="C18" s="131">
         <v>89844</v>
       </c>
-      <c r="D18" s="130">
+      <c r="D18" s="131">
         <v>357</v>
       </c>
-      <c r="E18" s="156">
+      <c r="E18" s="158">
         <v>2013</v>
       </c>
       <c r="F18" s="37"/>
@@ -4325,16 +4392,16 @@
       <c r="A19" s="65">
         <v>2014</v>
       </c>
-      <c r="B19" s="129">
+      <c r="B19" s="130">
         <v>127492</v>
       </c>
-      <c r="C19" s="130">
+      <c r="C19" s="131">
         <v>79392</v>
       </c>
-      <c r="D19" s="130">
+      <c r="D19" s="131">
         <v>357</v>
       </c>
-      <c r="E19" s="156">
+      <c r="E19" s="158">
         <v>2014</v>
       </c>
       <c r="F19" s="37"/>
@@ -4343,16 +4410,16 @@
       <c r="A20" s="65">
         <v>2015</v>
       </c>
-      <c r="B20" s="129">
+      <c r="B20" s="130">
         <v>92206</v>
       </c>
-      <c r="C20" s="130">
+      <c r="C20" s="131">
         <v>63786</v>
       </c>
-      <c r="D20" s="130">
+      <c r="D20" s="131">
         <v>355</v>
       </c>
-      <c r="E20" s="156">
+      <c r="E20" s="158">
         <v>2015</v>
       </c>
       <c r="F20" s="37"/>
@@ -4361,16 +4428,16 @@
       <c r="A21" s="65">
         <v>2016</v>
       </c>
-      <c r="B21" s="129">
+      <c r="B21" s="130">
         <v>134065</v>
       </c>
-      <c r="C21" s="130">
+      <c r="C21" s="131">
         <v>71956</v>
       </c>
-      <c r="D21" s="130">
+      <c r="D21" s="131">
         <v>1882</v>
       </c>
-      <c r="E21" s="156">
+      <c r="E21" s="158">
         <v>2016</v>
       </c>
       <c r="F21" s="37"/>
@@ -4379,16 +4446,16 @@
       <c r="A22" s="65">
         <v>2017</v>
       </c>
-      <c r="B22" s="129">
+      <c r="B22" s="130">
         <v>141002</v>
       </c>
-      <c r="C22" s="130">
+      <c r="C22" s="131">
         <v>94451</v>
       </c>
-      <c r="D22" s="130">
+      <c r="D22" s="131">
         <v>2727</v>
       </c>
-      <c r="E22" s="156">
+      <c r="E22" s="158">
         <v>2017</v>
       </c>
       <c r="F22" s="37"/>
@@ -4397,16 +4464,16 @@
       <c r="A23" s="65">
         <v>2018</v>
       </c>
-      <c r="B23" s="129">
+      <c r="B23" s="130">
         <v>157130</v>
       </c>
-      <c r="C23" s="129">
+      <c r="C23" s="130">
         <v>94280</v>
       </c>
-      <c r="D23" s="130">
+      <c r="D23" s="131">
         <v>3278</v>
       </c>
-      <c r="E23" s="156">
+      <c r="E23" s="158">
         <v>2018</v>
       </c>
       <c r="F23" s="37"/>
@@ -4415,16 +4482,16 @@
       <c r="A24" s="69">
         <v>2019</v>
       </c>
-      <c r="B24" s="129">
+      <c r="B24" s="130">
         <v>165016</v>
       </c>
-      <c r="C24" s="129">
+      <c r="C24" s="130">
         <v>110634</v>
       </c>
-      <c r="D24" s="130">
+      <c r="D24" s="131">
         <v>4405</v>
       </c>
-      <c r="E24" s="156">
+      <c r="E24" s="158">
         <v>2019</v>
       </c>
       <c r="F24" s="37"/>
@@ -4433,16 +4500,16 @@
       <c r="A25" s="69">
         <v>2020</v>
       </c>
-      <c r="B25" s="129">
+      <c r="B25" s="130">
         <v>83787</v>
       </c>
-      <c r="C25" s="129">
+      <c r="C25" s="130">
         <v>125071</v>
       </c>
-      <c r="D25" s="130">
+      <c r="D25" s="131">
         <v>6809</v>
       </c>
-      <c r="E25" s="156">
+      <c r="E25" s="158">
         <v>2020</v>
       </c>
       <c r="F25" s="37"/>
@@ -4451,16 +4518,16 @@
       <c r="A26" s="69">
         <v>2021</v>
       </c>
-      <c r="B26" s="129">
+      <c r="B26" s="130">
         <v>62925</v>
       </c>
-      <c r="C26" s="129">
+      <c r="C26" s="130">
         <v>138018</v>
       </c>
-      <c r="D26" s="130">
+      <c r="D26" s="131">
         <v>8411</v>
       </c>
-      <c r="E26" s="156">
+      <c r="E26" s="158">
         <v>2021</v>
       </c>
       <c r="F26" s="37"/>
@@ -4469,16 +4536,16 @@
       <c r="A27" s="69">
         <v>2022</v>
       </c>
-      <c r="B27" s="129">
+      <c r="B27" s="130">
         <v>86268</v>
       </c>
-      <c r="C27" s="131">
+      <c r="C27" s="132">
         <v>47896.666666666664</v>
       </c>
-      <c r="D27" s="132">
+      <c r="D27" s="133">
         <v>17929</v>
       </c>
-      <c r="E27" s="156">
+      <c r="E27" s="158">
         <v>2022</v>
       </c>
       <c r="F27" s="37"/>
@@ -4487,16 +4554,16 @@
       <c r="A28" s="69">
         <v>2023</v>
       </c>
-      <c r="B28" s="129">
+      <c r="B28" s="130">
         <v>108942</v>
       </c>
-      <c r="C28" s="131">
+      <c r="C28" s="132">
         <v>59744.75</v>
       </c>
-      <c r="D28" s="132">
+      <c r="D28" s="133">
         <v>53765</v>
       </c>
-      <c r="E28" s="156">
+      <c r="E28" s="158">
         <v>2023</v>
       </c>
       <c r="F28" s="37"/>
@@ -4505,207 +4572,245 @@
       <c r="A29" s="69">
         <v>2024</v>
       </c>
-      <c r="B29" s="131">
+      <c r="B29" s="132">
         <v>174335</v>
       </c>
-      <c r="C29" s="131">
+      <c r="C29" s="132">
         <v>102549</v>
       </c>
-      <c r="D29" s="132">
+      <c r="D29" s="133">
         <v>214822</v>
       </c>
-      <c r="E29" s="157">
+      <c r="E29" s="159">
         <v>2024</v>
       </c>
-      <c r="F29" s="140"/>
+      <c r="F29" s="141"/>
     </row>
     <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="151">
+      <c r="A30" s="152">
         <v>2025</v>
       </c>
-      <c r="B30" s="152">
+      <c r="B30" s="153">
         <v>153847</v>
       </c>
-      <c r="C30" s="153">
+      <c r="C30" s="154">
         <v>103654</v>
       </c>
-      <c r="D30" s="154">
+      <c r="D30" s="155">
         <v>276943.95097767573</v>
       </c>
-      <c r="E30" s="157">
+      <c r="E30" s="159">
         <v>2025</v>
       </c>
-      <c r="F30" s="140"/>
+      <c r="F30" s="141"/>
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="150">
+      <c r="A31" s="151">
         <v>46023</v>
       </c>
-      <c r="B31" s="167" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" s="145">
+      <c r="B31" s="172" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" s="146">
         <v>103434</v>
       </c>
-      <c r="D31" s="146">
+      <c r="D31" s="147">
         <v>291649.69882649806</v>
       </c>
-      <c r="E31" s="158">
+      <c r="E31" s="160">
         <v>46023</v>
       </c>
-      <c r="F31" s="149"/>
+      <c r="F31" s="150"/>
     </row>
     <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="150">
+      <c r="A32" s="151">
         <v>46054</v>
       </c>
-      <c r="B32" s="168"/>
-      <c r="C32" s="145">
+      <c r="B32" s="173"/>
+      <c r="C32" s="146">
         <v>104188</v>
       </c>
-      <c r="D32" s="146">
+      <c r="D32" s="147">
         <v>296423.44646341231</v>
       </c>
-      <c r="E32" s="158">
+      <c r="E32" s="160">
         <v>46054</v>
       </c>
-      <c r="F32" s="149"/>
+      <c r="F32" s="150"/>
     </row>
     <row r="33" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="150">
+      <c r="A33" s="151">
         <v>46082</v>
       </c>
-      <c r="B33" s="168"/>
-      <c r="C33" s="145">
+      <c r="B33" s="173"/>
+      <c r="C33" s="146">
         <v>104550</v>
       </c>
-      <c r="D33" s="146">
+      <c r="D33" s="147">
         <v>300556.70016996656</v>
       </c>
-      <c r="E33" s="158">
+      <c r="E33" s="160">
         <v>46082</v>
       </c>
-      <c r="F33" s="149"/>
+      <c r="F33" s="150"/>
     </row>
     <row r="34" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="150">
+      <c r="A34" s="151">
         <v>46113</v>
       </c>
-      <c r="B34" s="168"/>
-      <c r="C34" s="145">
+      <c r="B34" s="173"/>
+      <c r="C34" s="146">
         <v>107572</v>
       </c>
-      <c r="D34" s="146">
+      <c r="D34" s="147">
         <v>305622.74967854086</v>
       </c>
-      <c r="E34" s="158">
+      <c r="E34" s="160">
         <v>46113</v>
       </c>
-      <c r="F34" s="149"/>
+      <c r="F34" s="150"/>
     </row>
     <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="150">
+      <c r="A35" s="151">
         <v>46143</v>
       </c>
-      <c r="B35" s="168"/>
-      <c r="C35" s="145">
+      <c r="B35" s="173"/>
+      <c r="C35" s="146">
         <v>113989</v>
       </c>
-      <c r="D35" s="146">
+      <c r="D35" s="147">
         <v>312238.53876198584</v>
       </c>
-      <c r="E35" s="158">
+      <c r="E35" s="160">
         <v>46143</v>
       </c>
-      <c r="F35" s="149"/>
+      <c r="F35" s="150"/>
     </row>
     <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="150">
+      <c r="A36" s="151">
         <v>46174</v>
       </c>
-      <c r="B36" s="169"/>
-      <c r="C36" s="145">
+      <c r="B36" s="173"/>
+      <c r="C36" s="146">
         <v>116641</v>
       </c>
-      <c r="D36" s="146">
+      <c r="D36" s="147">
         <v>316934.69872540527</v>
       </c>
-      <c r="E36" s="158">
+      <c r="E36" s="160">
         <v>46174</v>
       </c>
-      <c r="F36" s="149"/>
-    </row>
-    <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="144"/>
-      <c r="B37" s="37"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" s="37"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="68" t="s">
-        <v>0</v>
-      </c>
-      <c r="B39" s="37"/>
-      <c r="C39" s="37"/>
-      <c r="D39" s="37"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="68" t="s">
-        <v>86</v>
-      </c>
+      <c r="F36" s="150"/>
+    </row>
+    <row r="37" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="151">
+        <v>46204</v>
+      </c>
+      <c r="B37" s="173"/>
+      <c r="C37" s="146">
+        <v>117451</v>
+      </c>
+      <c r="D37" s="147">
+        <v>320826.52290768066</v>
+      </c>
+      <c r="E37" s="160">
+        <v>46204</v>
+      </c>
+      <c r="F37" s="150"/>
+    </row>
+    <row r="38" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="151">
+        <v>46235</v>
+      </c>
+      <c r="B38" s="173"/>
+      <c r="C38" s="146">
+        <v>123648</v>
+      </c>
+      <c r="D38" s="147">
+        <v>325966.85453771998</v>
+      </c>
+      <c r="E38" s="160">
+        <v>46235</v>
+      </c>
+      <c r="F38" s="150"/>
+    </row>
+    <row r="39" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="151">
+        <v>46266</v>
+      </c>
+      <c r="B39" s="174"/>
+      <c r="C39" s="146">
+        <v>127613</v>
+      </c>
+      <c r="D39" s="147">
+        <v>325367.72977980302</v>
+      </c>
+      <c r="E39" s="160">
+        <v>46266</v>
+      </c>
+      <c r="F39" s="150"/>
+    </row>
+    <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="145"/>
       <c r="B40" s="37"/>
       <c r="C40" s="37"/>
       <c r="D40" s="37"/>
     </row>
-    <row r="41" spans="1:6" s="11" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="94"/>
-      <c r="B41" s="94"/>
-      <c r="C41" s="94"/>
-      <c r="D41" s="94"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-    </row>
-    <row r="42" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-    </row>
-    <row r="43" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="15"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-    </row>
-    <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="95" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="37"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="37"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" s="68" t="s">
         <v>85</v>
       </c>
+      <c r="B43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+    </row>
+    <row r="44" spans="1:6" s="11" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="95"/>
       <c r="B44" s="95"/>
       <c r="C44" s="95"/>
       <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
-      <c r="F44" s="95"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="11"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="11"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="11"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+    </row>
+    <row r="45" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+    </row>
+    <row r="46" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="15"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+    </row>
+    <row r="47" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="96" t="s">
+        <v>84</v>
+      </c>
+      <c r="B47" s="96"/>
+      <c r="C47" s="96"/>
+      <c r="D47" s="96"/>
+      <c r="E47" s="96"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="11"/>
@@ -4765,43 +4870,43 @@
       <c r="A66" s="11"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="24" t="s">
+      <c r="A67" s="11"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="11"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="11"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B67" s="37"/>
-      <c r="C67" s="37"/>
-      <c r="D67" s="37"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="68" t="s">
+      <c r="B70" s="37"/>
+      <c r="C70" s="37"/>
+      <c r="D70" s="37"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B68" s="37"/>
-      <c r="C68" s="37"/>
-      <c r="D68" s="37"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="141"/>
-      <c r="B69" s="141"/>
-      <c r="C69" s="141"/>
-      <c r="D69" s="141"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="143" t="s">
-        <v>79</v>
-      </c>
-      <c r="B70" s="11"/>
-      <c r="C70" s="11"/>
-      <c r="D70" s="11"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="11"/>
+      <c r="B71" s="37"/>
+      <c r="C71" s="37"/>
+      <c r="D71" s="37"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="11"/>
+      <c r="A72" s="142"/>
+      <c r="B72" s="142"/>
+      <c r="C72" s="142"/>
+      <c r="D72" s="142"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="11"/>
+      <c r="A73" s="144" t="s">
+        <v>78</v>
+      </c>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="11"/>
@@ -5370,16 +5475,25 @@
     <row r="262" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A262" s="11"/>
     </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A263" s="11"/>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A264" s="11"/>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A265" s="11"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="B31:B39"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
   </mergeCells>
-  <phoneticPr fontId="44" type="noConversion"/>
+  <phoneticPr fontId="45" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="E1" location="Indice!A1" display="volver al índice"/>
   </hyperlinks>
@@ -5418,14 +5532,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="16" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="175" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
+      <c r="A1" s="180" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
       <c r="G1" s="71" t="s">
         <v>18</v>
       </c>
@@ -5457,7 +5571,7 @@
     </row>
     <row r="4" spans="1:10" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="40"/>
-      <c r="C4" s="136"/>
+      <c r="C4" s="137"/>
       <c r="D4" s="41"/>
       <c r="E4" s="21"/>
       <c r="F4" s="21"/>
@@ -5473,10 +5587,10 @@
         <v>33</v>
       </c>
       <c r="D5" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="42" t="s">
         <v>76</v>
-      </c>
-      <c r="E5" s="42" t="s">
-        <v>77</v>
       </c>
       <c r="F5" s="36"/>
       <c r="G5" s="9"/>
@@ -5488,14 +5602,14 @@
       <c r="B6" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="108">
-        <v>116641</v>
-      </c>
-      <c r="D6" s="108">
-        <v>79045</v>
-      </c>
-      <c r="E6" s="109">
-        <v>37596</v>
+      <c r="C6" s="109">
+        <v>127613</v>
+      </c>
+      <c r="D6" s="109">
+        <v>86288</v>
+      </c>
+      <c r="E6" s="110">
+        <v>41325</v>
       </c>
       <c r="F6" s="76"/>
       <c r="G6" s="74"/>
@@ -5507,22 +5621,22 @@
       <c r="B7" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="110">
-        <v>147</v>
-      </c>
-      <c r="D7" s="110">
-        <v>109</v>
-      </c>
-      <c r="E7" s="111">
-        <v>38</v>
+      <c r="C7" s="111">
+        <v>143</v>
+      </c>
+      <c r="D7" s="111">
+        <v>116</v>
+      </c>
+      <c r="E7" s="112">
+        <v>27</v>
       </c>
       <c r="F7" s="77"/>
       <c r="G7" s="78"/>
-      <c r="H7" s="159">
-        <v>-109</v>
-      </c>
-      <c r="I7" s="160">
-        <v>38</v>
+      <c r="H7" s="161">
+        <v>-116</v>
+      </c>
+      <c r="I7" s="162">
+        <v>27</v>
       </c>
       <c r="J7" s="75"/>
     </row>
@@ -5530,22 +5644,22 @@
       <c r="B8" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="110">
-        <v>6113</v>
-      </c>
-      <c r="D8" s="110">
-        <v>4053</v>
-      </c>
-      <c r="E8" s="111">
-        <v>2060</v>
+      <c r="C8" s="111">
+        <v>6420</v>
+      </c>
+      <c r="D8" s="111">
+        <v>4291</v>
+      </c>
+      <c r="E8" s="112">
+        <v>2129</v>
       </c>
       <c r="F8" s="77"/>
       <c r="G8" s="78"/>
-      <c r="H8" s="159">
-        <v>-4053</v>
-      </c>
-      <c r="I8" s="160">
-        <v>2060</v>
+      <c r="H8" s="161">
+        <v>-4291</v>
+      </c>
+      <c r="I8" s="162">
+        <v>2129</v>
       </c>
       <c r="J8" s="75"/>
     </row>
@@ -5553,22 +5667,22 @@
       <c r="B9" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="110">
-        <v>13266</v>
-      </c>
-      <c r="D9" s="110">
-        <v>8484</v>
-      </c>
-      <c r="E9" s="111">
-        <v>4782</v>
+      <c r="C9" s="111">
+        <v>14363</v>
+      </c>
+      <c r="D9" s="111">
+        <v>8991</v>
+      </c>
+      <c r="E9" s="112">
+        <v>5372</v>
       </c>
       <c r="F9" s="77"/>
       <c r="G9" s="78"/>
-      <c r="H9" s="159">
-        <v>-8484</v>
-      </c>
-      <c r="I9" s="160">
-        <v>4782</v>
+      <c r="H9" s="161">
+        <v>-8991</v>
+      </c>
+      <c r="I9" s="162">
+        <v>5372</v>
       </c>
       <c r="J9" s="75"/>
     </row>
@@ -5576,22 +5690,22 @@
       <c r="B10" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="110">
-        <v>15887</v>
-      </c>
-      <c r="D10" s="110">
-        <v>10286</v>
-      </c>
-      <c r="E10" s="111">
-        <v>5601</v>
+      <c r="C10" s="111">
+        <v>17437</v>
+      </c>
+      <c r="D10" s="111">
+        <v>11269</v>
+      </c>
+      <c r="E10" s="112">
+        <v>6168</v>
       </c>
       <c r="F10" s="77"/>
       <c r="G10" s="78"/>
-      <c r="H10" s="159">
-        <v>-10286</v>
-      </c>
-      <c r="I10" s="160">
-        <v>5601</v>
+      <c r="H10" s="161">
+        <v>-11269</v>
+      </c>
+      <c r="I10" s="162">
+        <v>6168</v>
       </c>
       <c r="J10" s="75"/>
     </row>
@@ -5599,22 +5713,22 @@
       <c r="B11" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="110">
-        <v>16189</v>
-      </c>
-      <c r="D11" s="110">
-        <v>10542</v>
-      </c>
-      <c r="E11" s="111">
-        <v>5647</v>
+      <c r="C11" s="111">
+        <v>17558</v>
+      </c>
+      <c r="D11" s="111">
+        <v>11369</v>
+      </c>
+      <c r="E11" s="112">
+        <v>6189</v>
       </c>
       <c r="F11" s="77"/>
       <c r="G11" s="78"/>
-      <c r="H11" s="159">
-        <v>-10542</v>
-      </c>
-      <c r="I11" s="160">
-        <v>5647</v>
+      <c r="H11" s="161">
+        <v>-11369</v>
+      </c>
+      <c r="I11" s="162">
+        <v>6189</v>
       </c>
       <c r="J11" s="75"/>
     </row>
@@ -5622,22 +5736,22 @@
       <c r="B12" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="110">
-        <v>14769</v>
-      </c>
-      <c r="D12" s="110">
-        <v>9841</v>
-      </c>
-      <c r="E12" s="111">
-        <v>4928</v>
+      <c r="C12" s="111">
+        <v>16158</v>
+      </c>
+      <c r="D12" s="111">
+        <v>10647</v>
+      </c>
+      <c r="E12" s="112">
+        <v>5511</v>
       </c>
       <c r="F12" s="77"/>
       <c r="G12" s="78"/>
-      <c r="H12" s="159">
-        <v>-9841</v>
-      </c>
-      <c r="I12" s="160">
-        <v>4928</v>
+      <c r="H12" s="161">
+        <v>-10647</v>
+      </c>
+      <c r="I12" s="162">
+        <v>5511</v>
       </c>
       <c r="J12" s="75"/>
     </row>
@@ -5645,22 +5759,22 @@
       <c r="B13" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="110">
-        <v>20034</v>
-      </c>
-      <c r="D13" s="110">
-        <v>13574</v>
-      </c>
-      <c r="E13" s="111">
-        <v>6460</v>
+      <c r="C13" s="111">
+        <v>22082</v>
+      </c>
+      <c r="D13" s="111">
+        <v>14949</v>
+      </c>
+      <c r="E13" s="112">
+        <v>7133</v>
       </c>
       <c r="F13" s="77"/>
       <c r="G13" s="78"/>
-      <c r="H13" s="159">
-        <v>-13574</v>
-      </c>
-      <c r="I13" s="160">
-        <v>6460</v>
+      <c r="H13" s="161">
+        <v>-14949</v>
+      </c>
+      <c r="I13" s="162">
+        <v>7133</v>
       </c>
       <c r="J13" s="75"/>
     </row>
@@ -5668,22 +5782,22 @@
       <c r="B14" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="110">
-        <v>15294</v>
-      </c>
-      <c r="D14" s="110">
-        <v>10492</v>
-      </c>
-      <c r="E14" s="111">
-        <v>4802</v>
+      <c r="C14" s="111">
+        <v>16842</v>
+      </c>
+      <c r="D14" s="111">
+        <v>11576</v>
+      </c>
+      <c r="E14" s="112">
+        <v>5266</v>
       </c>
       <c r="F14" s="77"/>
       <c r="G14" s="78"/>
-      <c r="H14" s="159">
-        <v>-10492</v>
-      </c>
-      <c r="I14" s="160">
-        <v>4802</v>
+      <c r="H14" s="161">
+        <v>-11576</v>
+      </c>
+      <c r="I14" s="162">
+        <v>5266</v>
       </c>
       <c r="J14" s="75"/>
     </row>
@@ -5691,22 +5805,22 @@
       <c r="B15" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="110">
-        <v>10092</v>
-      </c>
-      <c r="D15" s="110">
-        <v>7102</v>
-      </c>
-      <c r="E15" s="111">
-        <v>2990</v>
+      <c r="C15" s="111">
+        <v>11162</v>
+      </c>
+      <c r="D15" s="111">
+        <v>7933</v>
+      </c>
+      <c r="E15" s="112">
+        <v>3229</v>
       </c>
       <c r="F15" s="77"/>
       <c r="G15" s="78"/>
-      <c r="H15" s="159">
-        <v>-7102</v>
-      </c>
-      <c r="I15" s="160">
-        <v>2990</v>
+      <c r="H15" s="161">
+        <v>-7933</v>
+      </c>
+      <c r="I15" s="162">
+        <v>3229</v>
       </c>
       <c r="J15" s="75"/>
     </row>
@@ -5714,22 +5828,22 @@
       <c r="B16" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="110">
-        <v>4850</v>
-      </c>
-      <c r="D16" s="110">
-        <v>4562</v>
-      </c>
-      <c r="E16" s="111">
-        <v>288</v>
+      <c r="C16" s="111">
+        <v>5448</v>
+      </c>
+      <c r="D16" s="111">
+        <v>5147</v>
+      </c>
+      <c r="E16" s="112">
+        <v>301</v>
       </c>
       <c r="F16" s="77"/>
       <c r="G16" s="79"/>
-      <c r="H16" s="159">
-        <v>-4562</v>
-      </c>
-      <c r="I16" s="160">
-        <v>288</v>
+      <c r="H16" s="161">
+        <v>-5147</v>
+      </c>
+      <c r="I16" s="162">
+        <v>301</v>
       </c>
       <c r="J16" s="75"/>
     </row>
@@ -5737,13 +5851,13 @@
       <c r="B17" s="29"/>
       <c r="F17" s="80"/>
       <c r="G17" s="81"/>
-      <c r="H17" s="161"/>
-      <c r="I17" s="161"/>
+      <c r="H17" s="72"/>
+      <c r="I17" s="72"/>
       <c r="J17" s="82"/>
     </row>
     <row r="18" spans="1:13" s="10" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="82"/>
@@ -5767,14 +5881,14 @@
       <c r="M19" s="17"/>
     </row>
     <row r="20" spans="1:13" s="10" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="175" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="175"/>
-      <c r="C20" s="175"/>
-      <c r="D20" s="175"/>
-      <c r="E20" s="175"/>
-      <c r="F20" s="175"/>
+      <c r="A20" s="180" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="180"/>
+      <c r="C20" s="180"/>
+      <c r="D20" s="180"/>
+      <c r="E20" s="180"/>
+      <c r="F20" s="180"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
@@ -5889,7 +6003,7 @@
     </row>
     <row r="34" spans="1:10" s="10" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
@@ -9197,7 +9311,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A20:F20"/>
   </mergeCells>
-  <phoneticPr fontId="44" type="noConversion"/>
+  <phoneticPr fontId="45" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G1" location="Indice!A1" display="volver al índice"/>
   </hyperlinks>
@@ -9228,7 +9342,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
@@ -9258,20 +9372,20 @@
     </row>
     <row r="3" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="49"/>
-      <c r="B3" s="137"/>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="137"/>
-      <c r="G3" s="137"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="137"/>
-      <c r="J3" s="137"/>
-      <c r="K3" s="137"/>
-      <c r="L3" s="137"/>
-      <c r="M3" s="137"/>
-      <c r="N3" s="155"/>
-      <c r="O3" s="137"/>
+      <c r="B3" s="138"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
+      <c r="G3" s="138"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="138"/>
+      <c r="L3" s="138"/>
+      <c r="M3" s="138"/>
+      <c r="N3" s="156"/>
+      <c r="O3" s="138"/>
     </row>
     <row r="4" spans="1:18" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50"/>
@@ -9294,7 +9408,7 @@
         <v>2019</v>
       </c>
       <c r="H4" s="52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I4" s="52">
         <v>2021</v>
@@ -9312,7 +9426,7 @@
         <v>2025</v>
       </c>
       <c r="N4" s="52" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
@@ -9335,1168 +9449,1168 @@
       <c r="A6" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="112">
+      <c r="B6" s="113">
         <v>127492</v>
       </c>
-      <c r="C6" s="112">
+      <c r="C6" s="113">
         <v>92206</v>
       </c>
-      <c r="D6" s="112">
+      <c r="D6" s="113">
         <v>134065</v>
       </c>
-      <c r="E6" s="112">
+      <c r="E6" s="113">
         <v>141002</v>
       </c>
-      <c r="F6" s="112">
+      <c r="F6" s="113">
         <v>157130</v>
       </c>
-      <c r="G6" s="112">
+      <c r="G6" s="113">
         <v>165016</v>
       </c>
-      <c r="H6" s="112">
+      <c r="H6" s="113">
         <v>83787</v>
       </c>
-      <c r="I6" s="112">
+      <c r="I6" s="113">
         <v>62925</v>
       </c>
-      <c r="J6" s="112">
+      <c r="J6" s="113">
         <v>86268</v>
       </c>
-      <c r="K6" s="112">
+      <c r="K6" s="113">
         <v>108942</v>
       </c>
-      <c r="L6" s="112">
+      <c r="L6" s="113">
         <v>174335</v>
       </c>
-      <c r="M6" s="112">
+      <c r="M6" s="113">
         <v>153847</v>
       </c>
-      <c r="N6" s="112">
-        <v>90634</v>
-      </c>
-      <c r="Q6" s="142"/>
+      <c r="N6" s="113">
+        <v>145004</v>
+      </c>
+      <c r="Q6" s="143"/>
     </row>
     <row r="7" spans="1:18" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="B7" s="113"/>
-      <c r="C7" s="114"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="114"/>
-      <c r="F7" s="115"/>
-      <c r="G7" s="115"/>
-      <c r="H7" s="115"/>
-      <c r="I7" s="115"/>
-      <c r="J7" s="115"/>
-      <c r="K7" s="115"/>
-      <c r="L7" s="115"/>
-      <c r="M7" s="115"/>
-      <c r="N7" s="115"/>
-      <c r="Q7" s="142"/>
+        <v>87</v>
+      </c>
+      <c r="B7" s="114"/>
+      <c r="C7" s="115"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="116"/>
+      <c r="K7" s="116"/>
+      <c r="L7" s="116"/>
+      <c r="M7" s="116"/>
+      <c r="N7" s="116"/>
+      <c r="Q7" s="143"/>
     </row>
     <row r="8" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="116">
+      <c r="B8" s="117">
         <v>1764</v>
       </c>
-      <c r="C8" s="116">
+      <c r="C8" s="117">
         <v>1437</v>
       </c>
-      <c r="D8" s="116">
+      <c r="D8" s="117">
         <v>1770</v>
       </c>
-      <c r="E8" s="116">
+      <c r="E8" s="117">
         <v>1801</v>
       </c>
-      <c r="F8" s="116">
+      <c r="F8" s="117">
         <v>1656</v>
       </c>
-      <c r="G8" s="116">
+      <c r="G8" s="117">
         <v>1613</v>
       </c>
-      <c r="H8" s="116">
+      <c r="H8" s="117">
         <v>692</v>
       </c>
-      <c r="I8" s="116">
+      <c r="I8" s="117">
         <v>762</v>
       </c>
-      <c r="J8" s="116">
+      <c r="J8" s="117">
         <v>1115</v>
       </c>
-      <c r="K8" s="116">
+      <c r="K8" s="117">
         <v>1441</v>
       </c>
-      <c r="L8" s="139">
+      <c r="L8" s="140">
         <v>1574</v>
       </c>
-      <c r="M8" s="139">
+      <c r="M8" s="140">
         <v>1616</v>
       </c>
-      <c r="N8" s="139">
-        <v>1131</v>
+      <c r="N8" s="140">
+        <v>1641</v>
       </c>
       <c r="O8" s="72"/>
       <c r="P8" s="72"/>
-      <c r="Q8" s="148"/>
-      <c r="R8" s="148"/>
+      <c r="Q8" s="149"/>
+      <c r="R8" s="149"/>
     </row>
     <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="116">
+      <c r="B9" s="117">
         <v>855</v>
       </c>
-      <c r="C9" s="116">
+      <c r="C9" s="117">
         <v>882</v>
       </c>
-      <c r="D9" s="116">
+      <c r="D9" s="117">
         <v>1415</v>
       </c>
-      <c r="E9" s="116">
+      <c r="E9" s="117">
         <v>1800</v>
       </c>
-      <c r="F9" s="116">
+      <c r="F9" s="117">
         <v>2011</v>
       </c>
-      <c r="G9" s="116">
+      <c r="G9" s="117">
         <v>1341</v>
       </c>
-      <c r="H9" s="116">
+      <c r="H9" s="117">
         <v>1124</v>
       </c>
-      <c r="I9" s="116">
+      <c r="I9" s="117">
         <v>734</v>
       </c>
-      <c r="J9" s="116">
+      <c r="J9" s="117">
         <v>1039</v>
       </c>
-      <c r="K9" s="116">
+      <c r="K9" s="117">
         <v>1335</v>
       </c>
-      <c r="L9" s="139">
+      <c r="L9" s="140">
         <v>2391</v>
       </c>
-      <c r="M9" s="139">
+      <c r="M9" s="140">
         <v>3423</v>
       </c>
-      <c r="N9" s="139">
-        <v>999</v>
+      <c r="N9" s="140">
+        <v>1588</v>
       </c>
       <c r="O9" s="72"/>
       <c r="P9" s="72"/>
-      <c r="Q9" s="148"/>
-      <c r="R9" s="148"/>
+      <c r="Q9" s="149"/>
+      <c r="R9" s="149"/>
     </row>
     <row r="10" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="116">
+      <c r="B10" s="117">
         <v>28130</v>
       </c>
-      <c r="C10" s="116">
+      <c r="C10" s="117">
         <v>19625</v>
       </c>
-      <c r="D10" s="116">
+      <c r="D10" s="117">
         <v>31156</v>
       </c>
-      <c r="E10" s="116">
+      <c r="E10" s="117">
         <v>32447</v>
       </c>
-      <c r="F10" s="116">
+      <c r="F10" s="117">
         <v>37982</v>
       </c>
-      <c r="G10" s="116">
+      <c r="G10" s="117">
         <v>35864</v>
       </c>
-      <c r="H10" s="116">
+      <c r="H10" s="117">
         <v>12362</v>
       </c>
-      <c r="I10" s="116">
+      <c r="I10" s="117">
         <v>9546</v>
       </c>
-      <c r="J10" s="116">
+      <c r="J10" s="117">
         <v>17437</v>
       </c>
-      <c r="K10" s="116">
+      <c r="K10" s="117">
         <v>22666</v>
       </c>
-      <c r="L10" s="139">
+      <c r="L10" s="140">
         <v>36233</v>
       </c>
-      <c r="M10" s="139">
+      <c r="M10" s="140">
         <v>36648</v>
       </c>
-      <c r="N10" s="139">
-        <v>22766</v>
+      <c r="N10" s="140">
+        <v>35922</v>
       </c>
       <c r="O10" s="72"/>
       <c r="P10" s="72"/>
-      <c r="Q10" s="148"/>
-      <c r="R10" s="148"/>
+      <c r="Q10" s="149"/>
+      <c r="R10" s="149"/>
     </row>
     <row r="11" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="116">
+      <c r="B11" s="117">
         <v>195</v>
       </c>
-      <c r="C11" s="116">
+      <c r="C11" s="117">
         <v>148</v>
       </c>
-      <c r="D11" s="116">
+      <c r="D11" s="117">
         <v>153</v>
       </c>
-      <c r="E11" s="116">
+      <c r="E11" s="117">
         <v>245</v>
       </c>
-      <c r="F11" s="116">
+      <c r="F11" s="117">
         <v>280</v>
       </c>
-      <c r="G11" s="116">
+      <c r="G11" s="117">
         <v>326</v>
       </c>
-      <c r="H11" s="116">
+      <c r="H11" s="117">
         <v>145</v>
       </c>
-      <c r="I11" s="116">
+      <c r="I11" s="117">
         <v>101</v>
       </c>
-      <c r="J11" s="116">
+      <c r="J11" s="117">
         <v>202</v>
       </c>
-      <c r="K11" s="116">
+      <c r="K11" s="117">
         <v>200</v>
       </c>
-      <c r="L11" s="139">
+      <c r="L11" s="140">
         <v>405</v>
       </c>
-      <c r="M11" s="139">
+      <c r="M11" s="140">
         <v>272</v>
       </c>
-      <c r="N11" s="139">
-        <v>151</v>
+      <c r="N11" s="140">
+        <v>254</v>
       </c>
       <c r="O11" s="72"/>
       <c r="P11" s="72"/>
-      <c r="Q11" s="148"/>
-      <c r="R11" s="148"/>
+      <c r="Q11" s="149"/>
+      <c r="R11" s="149"/>
     </row>
     <row r="12" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="116">
+      <c r="B12" s="117">
         <v>348</v>
       </c>
-      <c r="C12" s="116">
+      <c r="C12" s="117">
         <v>328</v>
       </c>
-      <c r="D12" s="116">
+      <c r="D12" s="117">
         <v>480</v>
       </c>
-      <c r="E12" s="116">
+      <c r="E12" s="117">
         <v>429</v>
       </c>
-      <c r="F12" s="116">
+      <c r="F12" s="117">
         <v>462</v>
       </c>
-      <c r="G12" s="116">
+      <c r="G12" s="117">
         <v>427</v>
       </c>
-      <c r="H12" s="116">
+      <c r="H12" s="117">
         <v>186</v>
       </c>
-      <c r="I12" s="116">
+      <c r="I12" s="117">
         <v>167</v>
       </c>
-      <c r="J12" s="116">
+      <c r="J12" s="117">
         <v>295</v>
       </c>
-      <c r="K12" s="116">
+      <c r="K12" s="117">
         <v>407</v>
       </c>
-      <c r="L12" s="139">
+      <c r="L12" s="140">
         <v>692</v>
       </c>
-      <c r="M12" s="139">
+      <c r="M12" s="140">
         <v>649</v>
       </c>
-      <c r="N12" s="139">
-        <v>380</v>
+      <c r="N12" s="140">
+        <v>556</v>
       </c>
       <c r="O12" s="72"/>
       <c r="P12" s="72"/>
-      <c r="Q12" s="148"/>
-      <c r="R12" s="148"/>
+      <c r="Q12" s="149"/>
+      <c r="R12" s="149"/>
     </row>
     <row r="13" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="116">
+      <c r="B13" s="117">
         <v>20270</v>
       </c>
-      <c r="C13" s="116">
+      <c r="C13" s="117">
         <v>14260</v>
       </c>
-      <c r="D13" s="116">
+      <c r="D13" s="117">
         <v>27363</v>
       </c>
-      <c r="E13" s="116">
+      <c r="E13" s="117">
         <v>22711</v>
       </c>
-      <c r="F13" s="116">
+      <c r="F13" s="117">
         <v>29561</v>
       </c>
-      <c r="G13" s="116">
+      <c r="G13" s="117">
         <v>34584</v>
       </c>
-      <c r="H13" s="116">
+      <c r="H13" s="117">
         <v>30113</v>
       </c>
-      <c r="I13" s="116">
+      <c r="I13" s="117">
         <v>13207</v>
       </c>
-      <c r="J13" s="116">
+      <c r="J13" s="117">
         <v>14196</v>
       </c>
-      <c r="K13" s="116">
+      <c r="K13" s="117">
         <v>24279</v>
       </c>
-      <c r="L13" s="139">
+      <c r="L13" s="140">
         <v>54046</v>
       </c>
-      <c r="M13" s="139">
+      <c r="M13" s="140">
         <v>25311</v>
       </c>
-      <c r="N13" s="139">
-        <v>13819</v>
+      <c r="N13" s="140">
+        <v>21663</v>
       </c>
       <c r="O13" s="72"/>
       <c r="P13" s="72"/>
-      <c r="Q13" s="148"/>
-      <c r="R13" s="148"/>
+      <c r="Q13" s="149"/>
+      <c r="R13" s="149"/>
     </row>
     <row r="14" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="116">
+      <c r="B14" s="117">
         <v>30297</v>
       </c>
-      <c r="C14" s="116">
+      <c r="C14" s="117">
         <v>22387</v>
       </c>
-      <c r="D14" s="116">
+      <c r="D14" s="117">
         <v>26718</v>
       </c>
-      <c r="E14" s="116">
+      <c r="E14" s="117">
         <v>30938</v>
       </c>
-      <c r="F14" s="116">
+      <c r="F14" s="117">
         <v>33766</v>
       </c>
-      <c r="G14" s="116">
+      <c r="G14" s="117">
         <v>36208</v>
       </c>
-      <c r="H14" s="116">
+      <c r="H14" s="117">
         <v>13105</v>
       </c>
-      <c r="I14" s="116">
+      <c r="I14" s="117">
         <v>12121</v>
       </c>
-      <c r="J14" s="116">
+      <c r="J14" s="117">
         <v>19329</v>
       </c>
-      <c r="K14" s="116">
+      <c r="K14" s="117">
         <v>21758</v>
       </c>
-      <c r="L14" s="139">
+      <c r="L14" s="140">
         <v>28790</v>
       </c>
-      <c r="M14" s="139">
+      <c r="M14" s="140">
         <v>32630</v>
       </c>
-      <c r="N14" s="139">
-        <v>20651</v>
+      <c r="N14" s="140">
+        <v>32928</v>
       </c>
       <c r="O14" s="72"/>
       <c r="P14" s="72"/>
-      <c r="Q14" s="148"/>
-      <c r="R14" s="148"/>
+      <c r="Q14" s="149"/>
+      <c r="R14" s="149"/>
     </row>
     <row r="15" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="116">
+      <c r="B15" s="117">
         <v>6149</v>
       </c>
-      <c r="C15" s="116">
+      <c r="C15" s="117">
         <v>4546</v>
       </c>
-      <c r="D15" s="116">
+      <c r="D15" s="117">
         <v>6224</v>
       </c>
-      <c r="E15" s="116">
+      <c r="E15" s="117">
         <v>6544</v>
       </c>
-      <c r="F15" s="116">
+      <c r="F15" s="117">
         <v>6623</v>
       </c>
-      <c r="G15" s="116">
+      <c r="G15" s="117">
         <v>7713</v>
       </c>
-      <c r="H15" s="116">
+      <c r="H15" s="117">
         <v>3349</v>
       </c>
-      <c r="I15" s="116">
+      <c r="I15" s="117">
         <v>2944</v>
       </c>
-      <c r="J15" s="116">
+      <c r="J15" s="117">
         <v>4000</v>
       </c>
-      <c r="K15" s="116">
+      <c r="K15" s="117">
         <v>5158</v>
       </c>
-      <c r="L15" s="139">
+      <c r="L15" s="140">
         <v>7158</v>
       </c>
-      <c r="M15" s="139">
+      <c r="M15" s="140">
         <v>7146</v>
       </c>
-      <c r="N15" s="139">
-        <v>4517</v>
+      <c r="N15" s="140">
+        <v>7810</v>
       </c>
       <c r="O15" s="72"/>
       <c r="P15" s="72"/>
-      <c r="Q15" s="148"/>
-      <c r="R15" s="148"/>
+      <c r="Q15" s="149"/>
+      <c r="R15" s="149"/>
     </row>
     <row r="16" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="116">
+      <c r="B16" s="117">
         <v>6861</v>
       </c>
-      <c r="C16" s="116">
+      <c r="C16" s="117">
         <v>5033</v>
       </c>
-      <c r="D16" s="116">
+      <c r="D16" s="117">
         <v>6374</v>
       </c>
-      <c r="E16" s="116">
+      <c r="E16" s="117">
         <v>7174</v>
       </c>
-      <c r="F16" s="116">
+      <c r="F16" s="117">
         <v>7277</v>
       </c>
-      <c r="G16" s="116">
+      <c r="G16" s="117">
         <v>7550</v>
       </c>
-      <c r="H16" s="116">
+      <c r="H16" s="117">
         <v>5049</v>
       </c>
-      <c r="I16" s="116">
+      <c r="I16" s="117">
         <v>4157</v>
       </c>
-      <c r="J16" s="116">
+      <c r="J16" s="117">
         <v>3379</v>
       </c>
-      <c r="K16" s="116">
+      <c r="K16" s="117">
         <v>4572</v>
       </c>
-      <c r="L16" s="139">
+      <c r="L16" s="140">
         <v>6493</v>
       </c>
-      <c r="M16" s="139">
+      <c r="M16" s="140">
         <v>7163</v>
       </c>
-      <c r="N16" s="139">
-        <v>4141</v>
+      <c r="N16" s="140">
+        <v>6564</v>
       </c>
       <c r="O16" s="72"/>
       <c r="P16" s="72"/>
-      <c r="Q16" s="148"/>
-      <c r="R16" s="148"/>
+      <c r="Q16" s="149"/>
+      <c r="R16" s="149"/>
     </row>
     <row r="17" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="116">
+      <c r="B17" s="117">
         <v>2379</v>
       </c>
-      <c r="C17" s="116">
+      <c r="C17" s="117">
         <v>1779</v>
       </c>
-      <c r="D17" s="116">
+      <c r="D17" s="117">
         <v>2923</v>
       </c>
-      <c r="E17" s="116">
+      <c r="E17" s="117">
         <v>2790</v>
       </c>
-      <c r="F17" s="116">
+      <c r="F17" s="117">
         <v>2917</v>
       </c>
-      <c r="G17" s="116">
+      <c r="G17" s="117">
         <v>2621</v>
       </c>
-      <c r="H17" s="116">
+      <c r="H17" s="117">
         <v>1381</v>
       </c>
-      <c r="I17" s="116">
+      <c r="I17" s="117">
         <v>598</v>
       </c>
-      <c r="J17" s="116">
+      <c r="J17" s="117">
         <v>1419</v>
       </c>
-      <c r="K17" s="116">
+      <c r="K17" s="117">
         <v>2188</v>
       </c>
-      <c r="L17" s="139">
+      <c r="L17" s="140">
         <v>3089</v>
       </c>
-      <c r="M17" s="139">
+      <c r="M17" s="140">
         <v>3944</v>
       </c>
-      <c r="N17" s="139">
-        <v>2382</v>
+      <c r="N17" s="140">
+        <v>4222</v>
       </c>
       <c r="O17" s="72"/>
       <c r="P17" s="72"/>
-      <c r="Q17" s="148"/>
-      <c r="R17" s="148"/>
+      <c r="Q17" s="149"/>
+      <c r="R17" s="149"/>
     </row>
     <row r="18" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="116">
+      <c r="B18" s="117">
         <v>2931</v>
       </c>
-      <c r="C18" s="116">
+      <c r="C18" s="117">
         <v>2066</v>
       </c>
-      <c r="D18" s="116">
+      <c r="D18" s="117">
         <v>3118</v>
       </c>
-      <c r="E18" s="116">
+      <c r="E18" s="117">
         <v>3364</v>
       </c>
-      <c r="F18" s="116">
+      <c r="F18" s="117">
         <v>3504</v>
       </c>
-      <c r="G18" s="116">
+      <c r="G18" s="117">
         <v>3661</v>
       </c>
-      <c r="H18" s="116">
+      <c r="H18" s="117">
         <v>1441</v>
       </c>
-      <c r="I18" s="116">
+      <c r="I18" s="117">
         <v>1026</v>
       </c>
-      <c r="J18" s="116">
+      <c r="J18" s="117">
         <v>2428</v>
       </c>
-      <c r="K18" s="116">
+      <c r="K18" s="117">
         <v>2461</v>
       </c>
-      <c r="L18" s="139">
+      <c r="L18" s="140">
         <v>3231</v>
       </c>
-      <c r="M18" s="139">
+      <c r="M18" s="140">
         <v>3154</v>
       </c>
-      <c r="N18" s="139">
-        <v>1884</v>
+      <c r="N18" s="140">
+        <v>2986</v>
       </c>
       <c r="O18" s="72"/>
       <c r="P18" s="72"/>
-      <c r="Q18" s="148"/>
-      <c r="R18" s="148"/>
+      <c r="Q18" s="149"/>
+      <c r="R18" s="149"/>
     </row>
     <row r="19" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="116">
+      <c r="B19" s="117">
         <v>935</v>
       </c>
-      <c r="C19" s="116">
+      <c r="C19" s="117">
         <v>699</v>
       </c>
-      <c r="D19" s="116">
+      <c r="D19" s="117">
         <v>783</v>
       </c>
-      <c r="E19" s="116">
+      <c r="E19" s="117">
         <v>922</v>
       </c>
-      <c r="F19" s="116">
+      <c r="F19" s="117">
         <v>1039</v>
       </c>
-      <c r="G19" s="116">
+      <c r="G19" s="117">
         <v>1085</v>
       </c>
-      <c r="H19" s="116">
+      <c r="H19" s="117">
         <v>433</v>
       </c>
-      <c r="I19" s="116">
+      <c r="I19" s="117">
         <v>421</v>
       </c>
-      <c r="J19" s="116">
+      <c r="J19" s="117">
         <v>557</v>
       </c>
-      <c r="K19" s="116">
+      <c r="K19" s="117">
         <v>605</v>
       </c>
-      <c r="L19" s="139">
+      <c r="L19" s="140">
         <v>637</v>
       </c>
-      <c r="M19" s="139">
+      <c r="M19" s="140">
         <v>684</v>
       </c>
-      <c r="N19" s="139">
-        <v>431</v>
+      <c r="N19" s="140">
+        <v>672</v>
       </c>
       <c r="O19" s="72"/>
       <c r="P19" s="72"/>
-      <c r="Q19" s="148"/>
-      <c r="R19" s="148"/>
+      <c r="Q19" s="149"/>
+      <c r="R19" s="149"/>
     </row>
     <row r="20" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="116">
+      <c r="B20" s="117">
         <v>3619</v>
       </c>
-      <c r="C20" s="116">
+      <c r="C20" s="117">
         <v>2556</v>
       </c>
-      <c r="D20" s="116">
+      <c r="D20" s="117">
         <v>3727</v>
       </c>
-      <c r="E20" s="116">
+      <c r="E20" s="117">
         <v>4091</v>
       </c>
-      <c r="F20" s="116">
+      <c r="F20" s="117">
         <v>3954</v>
       </c>
-      <c r="G20" s="116">
+      <c r="G20" s="117">
         <v>4193</v>
       </c>
-      <c r="H20" s="116">
+      <c r="H20" s="117">
         <v>2215</v>
       </c>
-      <c r="I20" s="116">
+      <c r="I20" s="117">
         <v>1519</v>
       </c>
-      <c r="J20" s="116">
+      <c r="J20" s="117">
         <v>1881</v>
       </c>
-      <c r="K20" s="116">
+      <c r="K20" s="117">
         <v>2271</v>
       </c>
-      <c r="L20" s="139">
+      <c r="L20" s="140">
         <v>3437</v>
       </c>
-      <c r="M20" s="139">
+      <c r="M20" s="140">
         <v>3218</v>
       </c>
-      <c r="N20" s="139">
-        <v>1823</v>
+      <c r="N20" s="140">
+        <v>2903</v>
       </c>
       <c r="O20" s="72"/>
       <c r="P20" s="72"/>
-      <c r="Q20" s="148"/>
-      <c r="R20" s="148"/>
+      <c r="Q20" s="149"/>
+      <c r="R20" s="149"/>
     </row>
     <row r="21" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="116">
+      <c r="B21" s="117">
         <v>11740</v>
       </c>
-      <c r="C21" s="116">
+      <c r="C21" s="117">
         <v>8150</v>
       </c>
-      <c r="D21" s="116">
+      <c r="D21" s="117">
         <v>11371</v>
       </c>
-      <c r="E21" s="116">
+      <c r="E21" s="117">
         <v>13854</v>
       </c>
-      <c r="F21" s="116">
+      <c r="F21" s="117">
         <v>13716</v>
       </c>
-      <c r="G21" s="116">
+      <c r="G21" s="117">
         <v>14992</v>
       </c>
-      <c r="H21" s="116">
+      <c r="H21" s="117">
         <v>6325</v>
       </c>
-      <c r="I21" s="116">
+      <c r="I21" s="117">
         <v>6313</v>
       </c>
-      <c r="J21" s="116">
+      <c r="J21" s="117">
         <v>9404</v>
       </c>
-      <c r="K21" s="116">
+      <c r="K21" s="117">
         <v>10618</v>
       </c>
-      <c r="L21" s="139">
+      <c r="L21" s="140">
         <v>14150</v>
       </c>
-      <c r="M21" s="139">
+      <c r="M21" s="140">
         <v>16452</v>
       </c>
-      <c r="N21" s="139">
-        <v>9250</v>
+      <c r="N21" s="140">
+        <v>15276</v>
       </c>
       <c r="O21" s="72"/>
       <c r="P21" s="72"/>
-      <c r="Q21" s="148"/>
-      <c r="R21" s="148"/>
+      <c r="Q21" s="149"/>
+      <c r="R21" s="149"/>
     </row>
     <row r="22" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="116">
+      <c r="B22" s="117">
         <v>131</v>
       </c>
-      <c r="C22" s="116">
+      <c r="C22" s="117">
         <v>76</v>
       </c>
-      <c r="D22" s="116">
+      <c r="D22" s="117">
         <v>353</v>
       </c>
-      <c r="E22" s="116">
+      <c r="E22" s="117">
         <v>277</v>
       </c>
-      <c r="F22" s="116">
+      <c r="F22" s="117">
         <v>393</v>
       </c>
-      <c r="G22" s="116">
+      <c r="G22" s="117">
         <v>284</v>
       </c>
-      <c r="H22" s="116">
+      <c r="H22" s="117">
         <v>80</v>
       </c>
-      <c r="I22" s="116">
+      <c r="I22" s="117">
         <v>65</v>
       </c>
-      <c r="J22" s="116">
+      <c r="J22" s="117">
         <v>121</v>
       </c>
-      <c r="K22" s="116">
+      <c r="K22" s="117">
         <v>124</v>
       </c>
-      <c r="L22" s="139">
+      <c r="L22" s="140">
         <v>537</v>
       </c>
-      <c r="M22" s="139">
+      <c r="M22" s="140">
         <v>423</v>
       </c>
-      <c r="N22" s="139">
-        <v>142</v>
+      <c r="N22" s="140">
+        <v>202</v>
       </c>
       <c r="O22" s="72"/>
       <c r="P22" s="72"/>
-      <c r="Q22" s="148"/>
-      <c r="R22" s="148"/>
+      <c r="Q22" s="149"/>
+      <c r="R22" s="149"/>
     </row>
     <row r="23" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="116">
+      <c r="B23" s="117">
         <v>208</v>
       </c>
-      <c r="C23" s="116">
+      <c r="C23" s="117">
         <v>177</v>
       </c>
-      <c r="D23" s="116">
+      <c r="D23" s="117">
         <v>204</v>
       </c>
-      <c r="E23" s="116">
+      <c r="E23" s="117">
         <v>297</v>
       </c>
-      <c r="F23" s="116">
+      <c r="F23" s="117">
         <v>289</v>
       </c>
-      <c r="G23" s="116">
+      <c r="G23" s="117">
         <v>351</v>
       </c>
-      <c r="H23" s="116">
+      <c r="H23" s="117">
         <v>219</v>
       </c>
-      <c r="I23" s="116">
+      <c r="I23" s="117">
         <v>199</v>
       </c>
-      <c r="J23" s="116">
+      <c r="J23" s="117">
         <v>216</v>
       </c>
-      <c r="K23" s="116">
+      <c r="K23" s="117">
         <v>260</v>
       </c>
-      <c r="L23" s="139">
+      <c r="L23" s="140">
         <v>351</v>
       </c>
-      <c r="M23" s="139">
+      <c r="M23" s="140">
         <v>311</v>
       </c>
-      <c r="N23" s="139">
-        <v>197</v>
+      <c r="N23" s="140">
+        <v>297</v>
       </c>
       <c r="O23" s="72"/>
       <c r="P23" s="72"/>
-      <c r="Q23" s="148"/>
-      <c r="R23" s="148"/>
+      <c r="Q23" s="149"/>
+      <c r="R23" s="149"/>
     </row>
     <row r="24" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="116">
+      <c r="B24" s="117">
         <v>4431</v>
       </c>
-      <c r="C24" s="116">
+      <c r="C24" s="117">
         <v>3497</v>
       </c>
-      <c r="D24" s="116">
+      <c r="D24" s="117">
         <v>3794</v>
       </c>
-      <c r="E24" s="116">
+      <c r="E24" s="117">
         <v>4579</v>
       </c>
-      <c r="F24" s="116">
+      <c r="F24" s="117">
         <v>5226</v>
       </c>
-      <c r="G24" s="116">
+      <c r="G24" s="117">
         <v>5143</v>
       </c>
-      <c r="H24" s="116">
+      <c r="H24" s="117">
         <v>2333</v>
       </c>
-      <c r="I24" s="116">
+      <c r="I24" s="117">
         <v>2680</v>
       </c>
-      <c r="J24" s="116">
+      <c r="J24" s="117">
         <v>4059</v>
       </c>
-      <c r="K24" s="116">
+      <c r="K24" s="117">
         <v>4066</v>
       </c>
-      <c r="L24" s="139">
+      <c r="L24" s="140">
         <v>5522</v>
       </c>
-      <c r="M24" s="139">
+      <c r="M24" s="140">
         <v>5490</v>
       </c>
-      <c r="N24" s="139">
-        <v>3068</v>
+      <c r="N24" s="140">
+        <v>4723</v>
       </c>
       <c r="O24" s="72"/>
       <c r="P24" s="72"/>
-      <c r="Q24" s="148"/>
-      <c r="R24" s="148"/>
+      <c r="Q24" s="149"/>
+      <c r="R24" s="149"/>
     </row>
     <row r="25" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="116">
+      <c r="B25" s="117">
         <v>1712</v>
       </c>
-      <c r="C25" s="116">
+      <c r="C25" s="117">
         <v>1297</v>
       </c>
-      <c r="D25" s="116">
+      <c r="D25" s="117">
         <v>1885</v>
       </c>
-      <c r="E25" s="116">
+      <c r="E25" s="117">
         <v>2087</v>
       </c>
-      <c r="F25" s="116">
+      <c r="F25" s="117">
         <v>1748</v>
       </c>
-      <c r="G25" s="116">
+      <c r="G25" s="117">
         <v>1854</v>
       </c>
-      <c r="H25" s="116">
+      <c r="H25" s="117">
         <v>825</v>
       </c>
-      <c r="I25" s="116">
+      <c r="I25" s="117">
         <v>660</v>
       </c>
-      <c r="J25" s="116">
+      <c r="J25" s="117">
         <v>1049</v>
       </c>
-      <c r="K25" s="116">
+      <c r="K25" s="117">
         <v>1104</v>
       </c>
-      <c r="L25" s="139">
+      <c r="L25" s="140">
         <v>1781</v>
       </c>
-      <c r="M25" s="139">
+      <c r="M25" s="140">
         <v>1638</v>
       </c>
-      <c r="N25" s="139">
-        <v>859</v>
+      <c r="N25" s="140">
+        <v>1433</v>
       </c>
       <c r="O25" s="72"/>
       <c r="P25" s="72"/>
-      <c r="Q25" s="148"/>
-      <c r="R25" s="148"/>
+      <c r="Q25" s="149"/>
+      <c r="R25" s="149"/>
     </row>
     <row r="26" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="116">
+      <c r="B26" s="117">
         <v>3851</v>
       </c>
-      <c r="C26" s="116">
+      <c r="C26" s="117">
         <v>2822</v>
       </c>
-      <c r="D26" s="116">
+      <c r="D26" s="117">
         <v>3510</v>
       </c>
-      <c r="E26" s="116">
+      <c r="E26" s="117">
         <v>3848</v>
       </c>
-      <c r="F26" s="116">
+      <c r="F26" s="117">
         <v>3993</v>
       </c>
-      <c r="G26" s="116">
+      <c r="G26" s="117">
         <v>4156</v>
       </c>
-      <c r="H26" s="116">
+      <c r="H26" s="117">
         <v>1683</v>
       </c>
-      <c r="I26" s="116">
+      <c r="I26" s="117">
         <v>1565</v>
       </c>
-      <c r="J26" s="116">
+      <c r="J26" s="117">
         <v>2738</v>
       </c>
-      <c r="K26" s="116">
+      <c r="K26" s="117">
         <v>2904</v>
       </c>
-      <c r="L26" s="139">
+      <c r="L26" s="140">
         <v>3210</v>
       </c>
-      <c r="M26" s="139">
+      <c r="M26" s="140">
         <v>3055</v>
       </c>
-      <c r="N26" s="139">
-        <v>1614</v>
+      <c r="N26" s="140">
+        <v>2643</v>
       </c>
       <c r="O26" s="72"/>
       <c r="P26" s="72"/>
-      <c r="Q26" s="148"/>
-      <c r="R26" s="148"/>
+      <c r="Q26" s="149"/>
+      <c r="R26" s="149"/>
     </row>
     <row r="27" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="116">
+      <c r="B27" s="117">
         <v>0</v>
       </c>
-      <c r="C27" s="116">
+      <c r="C27" s="117">
         <v>0</v>
       </c>
-      <c r="D27" s="116">
+      <c r="D27" s="117">
         <v>0</v>
       </c>
-      <c r="E27" s="116">
+      <c r="E27" s="117">
         <v>0</v>
       </c>
-      <c r="F27" s="116">
+      <c r="F27" s="117">
         <v>2</v>
       </c>
-      <c r="G27" s="116">
+      <c r="G27" s="117">
         <v>1</v>
       </c>
-      <c r="H27" s="116">
+      <c r="H27" s="117">
         <v>0</v>
       </c>
-      <c r="I27" s="116">
+      <c r="I27" s="117">
         <v>0</v>
       </c>
-      <c r="J27" s="116">
+      <c r="J27" s="117">
         <v>1</v>
       </c>
-      <c r="K27" s="116">
+      <c r="K27" s="117">
         <v>0</v>
       </c>
-      <c r="L27" s="139">
+      <c r="L27" s="140">
         <v>0</v>
       </c>
-      <c r="M27" s="139">
+      <c r="M27" s="140">
         <v>0</v>
       </c>
-      <c r="N27" s="139">
+      <c r="N27" s="140">
         <v>0</v>
       </c>
       <c r="O27" s="72"/>
       <c r="P27" s="72"/>
-      <c r="Q27" s="148"/>
-      <c r="R27" s="148"/>
+      <c r="Q27" s="149"/>
+      <c r="R27" s="149"/>
     </row>
     <row r="28" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="116">
+      <c r="B28" s="117">
         <v>4</v>
       </c>
-      <c r="C28" s="116">
+      <c r="C28" s="117">
         <v>8</v>
       </c>
-      <c r="D28" s="116">
+      <c r="D28" s="117">
         <v>13</v>
       </c>
-      <c r="E28" s="116">
+      <c r="E28" s="117">
         <v>12</v>
       </c>
-      <c r="F28" s="116">
+      <c r="F28" s="117">
         <v>9</v>
       </c>
-      <c r="G28" s="116">
+      <c r="G28" s="117">
         <v>14</v>
       </c>
-      <c r="H28" s="116">
+      <c r="H28" s="117">
         <v>3</v>
       </c>
-      <c r="I28" s="116">
+      <c r="I28" s="117">
         <v>3</v>
       </c>
-      <c r="J28" s="116">
+      <c r="J28" s="117">
         <v>13</v>
       </c>
-      <c r="K28" s="116">
+      <c r="K28" s="117">
         <v>14</v>
       </c>
-      <c r="L28" s="139">
+      <c r="L28" s="140">
         <v>16</v>
       </c>
-      <c r="M28" s="139">
+      <c r="M28" s="140">
         <v>14</v>
       </c>
-      <c r="N28" s="139">
-        <v>7</v>
+      <c r="N28" s="140">
+        <v>9</v>
       </c>
       <c r="O28" s="72"/>
       <c r="P28" s="72"/>
-      <c r="Q28" s="148"/>
-      <c r="R28" s="148"/>
+      <c r="Q28" s="149"/>
+      <c r="R28" s="149"/>
     </row>
     <row r="29" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="116">
+      <c r="B29" s="117">
         <v>6</v>
       </c>
-      <c r="C29" s="116">
+      <c r="C29" s="117">
         <v>3</v>
       </c>
-      <c r="D29" s="116">
+      <c r="D29" s="117">
         <v>8</v>
       </c>
-      <c r="E29" s="116">
+      <c r="E29" s="117">
         <v>7</v>
       </c>
-      <c r="F29" s="116">
+      <c r="F29" s="117">
         <v>5</v>
       </c>
-      <c r="G29" s="116">
+      <c r="G29" s="117">
         <v>9</v>
       </c>
-      <c r="H29" s="116">
+      <c r="H29" s="117">
         <v>5</v>
       </c>
-      <c r="I29" s="116">
+      <c r="I29" s="117">
         <v>9</v>
       </c>
-      <c r="J29" s="116">
+      <c r="J29" s="117">
         <v>11</v>
       </c>
-      <c r="K29" s="116">
+      <c r="K29" s="117">
         <v>4</v>
       </c>
-      <c r="L29" s="139">
+      <c r="L29" s="140">
         <v>12</v>
       </c>
-      <c r="M29" s="139">
+      <c r="M29" s="140">
         <v>11</v>
       </c>
-      <c r="N29" s="139">
-        <v>8</v>
+      <c r="N29" s="140">
+        <v>13</v>
       </c>
       <c r="O29" s="73"/>
       <c r="P29" s="73"/>
-      <c r="Q29" s="148"/>
-      <c r="R29" s="148"/>
+      <c r="Q29" s="149"/>
+      <c r="R29" s="149"/>
     </row>
     <row r="30" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="B30" s="116">
+        <v>88</v>
+      </c>
+      <c r="B30" s="117">
         <v>676</v>
       </c>
-      <c r="C30" s="116">
+      <c r="C30" s="117">
         <v>430</v>
       </c>
-      <c r="D30" s="116">
+      <c r="D30" s="117">
         <v>723</v>
       </c>
-      <c r="E30" s="116">
+      <c r="E30" s="117">
         <v>785</v>
       </c>
-      <c r="F30" s="116">
+      <c r="F30" s="117">
         <v>717</v>
       </c>
-      <c r="G30" s="116">
+      <c r="G30" s="117">
         <v>1026</v>
       </c>
-      <c r="H30" s="116">
+      <c r="H30" s="117">
         <v>719</v>
       </c>
-      <c r="I30" s="116">
+      <c r="I30" s="117">
         <v>4128</v>
       </c>
-      <c r="J30" s="116">
+      <c r="J30" s="117">
         <v>1379</v>
       </c>
-      <c r="K30" s="116">
+      <c r="K30" s="117">
         <v>507</v>
       </c>
-      <c r="L30" s="139">
+      <c r="L30" s="140">
         <v>580</v>
       </c>
-      <c r="M30" s="139">
+      <c r="M30" s="140">
         <v>595</v>
       </c>
-      <c r="N30" s="139">
-        <v>414</v>
+      <c r="N30" s="140">
+        <v>699</v>
       </c>
       <c r="P30" s="72"/>
-      <c r="Q30" s="148"/>
-      <c r="R30" s="148"/>
+      <c r="Q30" s="149"/>
+      <c r="R30" s="149"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="47"/>
@@ -10531,7 +10645,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="22" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -10542,7 +10656,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="19" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -10554,12 +10668,12 @@
     <row r="36" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B37" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="44" type="noConversion"/>
+  <phoneticPr fontId="45" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="O1" location="Indice!A1" display="volver al índice"/>
   </hyperlinks>
@@ -10586,26 +10700,25 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.140625" style="84" customWidth="1"/>
-    <col min="2" max="3" width="11.7109375" style="84" customWidth="1"/>
-    <col min="4" max="4" width="13" style="84" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="84" customWidth="1"/>
+    <col min="2" max="4" width="13.7109375" style="84" customWidth="1"/>
+    <col min="5" max="5" width="14" style="163" customWidth="1"/>
     <col min="6" max="6" width="23.5703125" style="84" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="15.7109375" style="84" customWidth="1"/>
     <col min="9" max="16384" width="11.5703125" style="84"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="176" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="176"/>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="178" t="s">
+      <c r="A1" s="181" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="183" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="83"/>
@@ -10613,544 +10726,553 @@
       <c r="H1" s="83"/>
     </row>
     <row r="2" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="177"/>
-      <c r="B2" s="177"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="178"/>
+      <c r="A2" s="182"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="183"/>
     </row>
     <row r="3" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="90"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-    </row>
-    <row r="4" spans="1:10" s="86" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="123" t="s">
+      <c r="A3" s="89"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+    </row>
+    <row r="4" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="90"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="164"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="134"/>
+    </row>
+    <row r="5" spans="1:10" s="85" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="124" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="125" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="125" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="126" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="165"/>
+      <c r="F5" s="135"/>
+      <c r="G5" s="136"/>
+      <c r="H5" s="86"/>
+      <c r="I5" s="87"/>
+      <c r="J5" s="87"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="127" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="118">
+        <v>127613</v>
+      </c>
+      <c r="C6" s="118">
+        <v>86288</v>
+      </c>
+      <c r="D6" s="119">
+        <v>41325</v>
+      </c>
+      <c r="F6" s="139"/>
+      <c r="G6" s="86"/>
+      <c r="H6" s="86"/>
+      <c r="I6" s="87"/>
+      <c r="J6" s="87"/>
+    </row>
+    <row r="7" spans="1:10" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="124" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="124" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" s="125" t="s">
-        <v>77</v>
-      </c>
-      <c r="E4" s="133"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="126" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="117">
-        <v>116641</v>
-      </c>
-      <c r="C5" s="117">
-        <v>79045</v>
-      </c>
-      <c r="D5" s="118">
-        <v>37596</v>
-      </c>
-      <c r="F5" s="138"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="88"/>
-      <c r="J5" s="88"/>
-    </row>
-    <row r="6" spans="1:10" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="91" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="119">
-        <v>7990</v>
-      </c>
-      <c r="C6" s="119">
-        <v>3988</v>
-      </c>
-      <c r="D6" s="120">
-        <v>4002</v>
-      </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="87"/>
-      <c r="H6" s="87"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
-    </row>
-    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="92" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="121">
-        <v>49899</v>
-      </c>
-      <c r="C7" s="121">
-        <v>33533</v>
-      </c>
-      <c r="D7" s="122">
-        <v>16366</v>
-      </c>
-      <c r="E7" s="85"/>
-      <c r="F7" s="138"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="88"/>
-      <c r="J7" s="88"/>
+      <c r="B7" s="120">
+        <v>9029</v>
+      </c>
+      <c r="C7" s="120">
+        <v>4514</v>
+      </c>
+      <c r="D7" s="121">
+        <v>4515</v>
+      </c>
+      <c r="E7" s="166"/>
+      <c r="F7" s="157"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="87"/>
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="92" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="122">
+        <v>54936</v>
+      </c>
+      <c r="C8" s="122">
+        <v>36906</v>
+      </c>
+      <c r="D8" s="123">
+        <v>18030</v>
+      </c>
+      <c r="E8" s="166"/>
+      <c r="F8" s="157"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="86"/>
+      <c r="I8" s="87"/>
+      <c r="J8" s="87"/>
+    </row>
+    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="122">
+        <v>1421</v>
+      </c>
+      <c r="C9" s="122">
+        <v>1062</v>
+      </c>
+      <c r="D9" s="123">
+        <v>359</v>
+      </c>
+      <c r="E9" s="166"/>
+      <c r="F9" s="157"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="87"/>
+    </row>
+    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="93" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="121">
-        <v>1450</v>
-      </c>
-      <c r="C8" s="121">
-        <v>1124</v>
-      </c>
-      <c r="D8" s="122">
-        <v>326</v>
-      </c>
-      <c r="E8" s="85"/>
-      <c r="F8" s="138"/>
-      <c r="G8" s="87"/>
-      <c r="H8" s="87"/>
-      <c r="I8" s="88"/>
-      <c r="J8" s="88"/>
-    </row>
-    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="93" t="s">
+      <c r="B10" s="122">
+        <v>1998</v>
+      </c>
+      <c r="C10" s="122">
+        <v>1446</v>
+      </c>
+      <c r="D10" s="123">
+        <v>552</v>
+      </c>
+      <c r="E10" s="166"/>
+      <c r="F10" s="157"/>
+      <c r="G10" s="86"/>
+      <c r="H10" s="86"/>
+      <c r="I10" s="87"/>
+      <c r="J10" s="87"/>
+    </row>
+    <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="121">
-        <v>1867</v>
-      </c>
-      <c r="C9" s="121">
-        <v>1350</v>
-      </c>
-      <c r="D9" s="122">
-        <v>517</v>
-      </c>
-      <c r="E9" s="85"/>
-      <c r="F9" s="138"/>
-      <c r="G9" s="87"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="88"/>
-      <c r="J9" s="88"/>
-    </row>
-    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="92" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="121">
-        <v>2879</v>
-      </c>
-      <c r="C10" s="121">
-        <v>1922</v>
-      </c>
-      <c r="D10" s="122">
-        <v>957</v>
-      </c>
-      <c r="E10" s="85"/>
-      <c r="F10" s="138"/>
-      <c r="G10" s="87"/>
-      <c r="H10" s="87"/>
-      <c r="I10" s="88"/>
-      <c r="J10" s="88"/>
-    </row>
-    <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="93" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="121">
-        <v>8707</v>
-      </c>
-      <c r="C11" s="121">
-        <v>5359</v>
-      </c>
-      <c r="D11" s="122">
-        <v>3348</v>
-      </c>
-      <c r="E11" s="85"/>
-      <c r="F11" s="138"/>
-      <c r="G11" s="87"/>
-      <c r="H11" s="87"/>
-      <c r="I11" s="88"/>
-      <c r="J11" s="88"/>
+      <c r="B11" s="122">
+        <v>2685</v>
+      </c>
+      <c r="C11" s="122">
+        <v>1775</v>
+      </c>
+      <c r="D11" s="123">
+        <v>910</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="157"/>
+      <c r="G11" s="86"/>
+      <c r="H11" s="86"/>
+      <c r="I11" s="87"/>
+      <c r="J11" s="87"/>
     </row>
     <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="93" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="121">
-        <v>2335</v>
-      </c>
-      <c r="C12" s="121">
-        <v>1969</v>
-      </c>
-      <c r="D12" s="122">
-        <v>366</v>
-      </c>
-      <c r="E12" s="85"/>
-      <c r="F12" s="138"/>
-      <c r="G12" s="87"/>
-      <c r="H12" s="87"/>
-      <c r="I12" s="88"/>
-      <c r="J12" s="88"/>
+        <v>55</v>
+      </c>
+      <c r="B12" s="122">
+        <v>9658</v>
+      </c>
+      <c r="C12" s="122">
+        <v>5951</v>
+      </c>
+      <c r="D12" s="123">
+        <v>3707</v>
+      </c>
+      <c r="E12" s="166"/>
+      <c r="F12" s="157"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
+      <c r="I12" s="87"/>
+      <c r="J12" s="87"/>
     </row>
     <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="92" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="121">
-        <v>2386</v>
-      </c>
-      <c r="C13" s="121">
-        <v>1645</v>
-      </c>
-      <c r="D13" s="122">
-        <v>741</v>
-      </c>
-      <c r="E13" s="85"/>
-      <c r="F13" s="138"/>
-      <c r="G13" s="87"/>
-      <c r="H13" s="87"/>
-      <c r="I13" s="88"/>
-      <c r="J13" s="88"/>
+      <c r="A13" s="93" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="122">
+        <v>2479</v>
+      </c>
+      <c r="C13" s="122">
+        <v>2034</v>
+      </c>
+      <c r="D13" s="123">
+        <v>445</v>
+      </c>
+      <c r="E13" s="166"/>
+      <c r="F13" s="157"/>
+      <c r="G13" s="86"/>
+      <c r="H13" s="86"/>
+      <c r="I13" s="87"/>
+      <c r="J13" s="87"/>
     </row>
     <row r="14" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="92" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="121">
-        <v>918</v>
-      </c>
-      <c r="C14" s="121">
-        <v>785</v>
-      </c>
-      <c r="D14" s="122">
-        <v>133</v>
-      </c>
-      <c r="E14" s="85"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="87"/>
-      <c r="H14" s="87"/>
-      <c r="I14" s="88"/>
-      <c r="J14" s="88"/>
+        <v>57</v>
+      </c>
+      <c r="B14" s="122">
+        <v>2746</v>
+      </c>
+      <c r="C14" s="122">
+        <v>1941</v>
+      </c>
+      <c r="D14" s="123">
+        <v>805</v>
+      </c>
+      <c r="E14" s="166"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="86"/>
+      <c r="I14" s="87"/>
+      <c r="J14" s="87"/>
     </row>
     <row r="15" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="92" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="121">
-        <v>1566</v>
-      </c>
-      <c r="C15" s="121">
-        <v>1289</v>
-      </c>
-      <c r="D15" s="122">
-        <v>277</v>
-      </c>
-      <c r="E15" s="85"/>
-      <c r="F15" s="138"/>
-      <c r="G15" s="87"/>
-      <c r="H15" s="87"/>
-      <c r="I15" s="88"/>
-      <c r="J15" s="88"/>
+        <v>58</v>
+      </c>
+      <c r="B15" s="122">
+        <v>811</v>
+      </c>
+      <c r="C15" s="122">
+        <v>648</v>
+      </c>
+      <c r="D15" s="123">
+        <v>163</v>
+      </c>
+      <c r="E15" s="166"/>
+      <c r="F15" s="157"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="86"/>
+      <c r="I15" s="87"/>
+      <c r="J15" s="87"/>
     </row>
     <row r="16" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="92" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" s="121">
-        <v>798</v>
-      </c>
-      <c r="C16" s="121">
-        <v>545</v>
-      </c>
-      <c r="D16" s="122">
-        <v>253</v>
-      </c>
-      <c r="E16" s="85"/>
-      <c r="F16" s="138"/>
-      <c r="G16" s="87"/>
-      <c r="H16" s="87"/>
-      <c r="I16" s="88"/>
-      <c r="J16" s="88"/>
+        <v>59</v>
+      </c>
+      <c r="B16" s="122">
+        <v>1576</v>
+      </c>
+      <c r="C16" s="122">
+        <v>1293</v>
+      </c>
+      <c r="D16" s="123">
+        <v>283</v>
+      </c>
+      <c r="E16" s="166"/>
+      <c r="F16" s="157"/>
+      <c r="G16" s="86"/>
+      <c r="H16" s="86"/>
+      <c r="I16" s="87"/>
+      <c r="J16" s="87"/>
     </row>
     <row r="17" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="92" t="s">
-        <v>62</v>
-      </c>
-      <c r="B17" s="121">
-        <v>996</v>
-      </c>
-      <c r="C17" s="121">
-        <v>649</v>
-      </c>
-      <c r="D17" s="122">
-        <v>347</v>
-      </c>
-      <c r="E17" s="85"/>
-      <c r="F17" s="138"/>
-      <c r="G17" s="87"/>
-      <c r="H17" s="87"/>
-      <c r="I17" s="88"/>
-      <c r="J17" s="88"/>
+        <v>60</v>
+      </c>
+      <c r="B17" s="122">
+        <v>778</v>
+      </c>
+      <c r="C17" s="122">
+        <v>515</v>
+      </c>
+      <c r="D17" s="123">
+        <v>263</v>
+      </c>
+      <c r="E17" s="166"/>
+      <c r="F17" s="157"/>
+      <c r="G17" s="86"/>
+      <c r="H17" s="86"/>
+      <c r="I17" s="87"/>
+      <c r="J17" s="87"/>
     </row>
     <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="93" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="121">
-        <v>5452</v>
-      </c>
-      <c r="C18" s="121">
-        <v>3681</v>
-      </c>
-      <c r="D18" s="122">
-        <v>1771</v>
-      </c>
-      <c r="E18" s="85"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="87"/>
-      <c r="H18" s="87"/>
-      <c r="I18" s="88"/>
-      <c r="J18" s="88"/>
+      <c r="A18" s="92" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="122">
+        <v>1014</v>
+      </c>
+      <c r="C18" s="122">
+        <v>660</v>
+      </c>
+      <c r="D18" s="123">
+        <v>354</v>
+      </c>
+      <c r="E18" s="166"/>
+      <c r="F18" s="157"/>
+      <c r="G18" s="86"/>
+      <c r="H18" s="86"/>
+      <c r="I18" s="87"/>
+      <c r="J18" s="87"/>
     </row>
     <row r="19" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="93" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" s="121">
-        <v>2382</v>
-      </c>
-      <c r="C19" s="121">
-        <v>1844</v>
-      </c>
-      <c r="D19" s="122">
-        <v>538</v>
-      </c>
-      <c r="E19" s="85"/>
-      <c r="F19" s="138"/>
-      <c r="G19" s="87"/>
-      <c r="H19" s="87"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="88"/>
+        <v>62</v>
+      </c>
+      <c r="B19" s="122">
+        <v>6407</v>
+      </c>
+      <c r="C19" s="122">
+        <v>4427</v>
+      </c>
+      <c r="D19" s="123">
+        <v>1980</v>
+      </c>
+      <c r="E19" s="166"/>
+      <c r="F19" s="157"/>
+      <c r="G19" s="86"/>
+      <c r="H19" s="86"/>
+      <c r="I19" s="87"/>
+      <c r="J19" s="87"/>
     </row>
     <row r="20" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="93" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="121">
-        <v>1621</v>
-      </c>
-      <c r="C20" s="121">
-        <v>1036</v>
-      </c>
-      <c r="D20" s="122">
-        <v>585</v>
-      </c>
-      <c r="E20" s="85"/>
-      <c r="F20" s="138"/>
-      <c r="G20" s="87"/>
-      <c r="H20" s="87"/>
-      <c r="I20" s="88"/>
-      <c r="J20" s="88"/>
+        <v>63</v>
+      </c>
+      <c r="B20" s="122">
+        <v>2592</v>
+      </c>
+      <c r="C20" s="122">
+        <v>1974</v>
+      </c>
+      <c r="D20" s="123">
+        <v>618</v>
+      </c>
+      <c r="E20" s="166"/>
+      <c r="F20" s="157"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="87"/>
+      <c r="J20" s="87"/>
     </row>
     <row r="21" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="92" t="s">
-        <v>66</v>
-      </c>
-      <c r="B21" s="121">
-        <v>1627</v>
-      </c>
-      <c r="C21" s="121">
-        <v>989</v>
-      </c>
-      <c r="D21" s="122">
+      <c r="A21" s="93" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="122">
+        <v>1703</v>
+      </c>
+      <c r="C21" s="122">
+        <v>1065</v>
+      </c>
+      <c r="D21" s="123">
         <v>638</v>
       </c>
-      <c r="E21" s="85"/>
-      <c r="F21" s="138"/>
-      <c r="G21" s="87"/>
-      <c r="H21" s="87"/>
-      <c r="I21" s="88"/>
-      <c r="J21" s="88"/>
+      <c r="E21" s="166"/>
+      <c r="F21" s="157"/>
+      <c r="G21" s="86"/>
+      <c r="H21" s="86"/>
+      <c r="I21" s="87"/>
+      <c r="J21" s="87"/>
     </row>
     <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="92" t="s">
-        <v>67</v>
-      </c>
-      <c r="B22" s="121">
-        <v>3362</v>
-      </c>
-      <c r="C22" s="121">
-        <v>2632</v>
-      </c>
-      <c r="D22" s="122">
-        <v>730</v>
-      </c>
-      <c r="E22" s="85"/>
-      <c r="F22" s="138"/>
-      <c r="G22" s="87"/>
-      <c r="H22" s="87"/>
-      <c r="I22" s="88"/>
-      <c r="J22" s="88"/>
+        <v>65</v>
+      </c>
+      <c r="B22" s="122">
+        <v>1748</v>
+      </c>
+      <c r="C22" s="122">
+        <v>1072</v>
+      </c>
+      <c r="D22" s="123">
+        <v>676</v>
+      </c>
+      <c r="E22" s="166"/>
+      <c r="F22" s="157"/>
+      <c r="G22" s="86"/>
+      <c r="H22" s="86"/>
+      <c r="I22" s="87"/>
+      <c r="J22" s="87"/>
     </row>
     <row r="23" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="93" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" s="121">
-        <v>2713</v>
-      </c>
-      <c r="C23" s="121">
-        <v>2080</v>
-      </c>
-      <c r="D23" s="122">
-        <v>633</v>
-      </c>
-      <c r="E23" s="85"/>
-      <c r="F23" s="138"/>
-      <c r="G23" s="87"/>
-      <c r="H23" s="87"/>
-      <c r="I23" s="88"/>
-      <c r="J23" s="88"/>
+      <c r="A23" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="122">
+        <v>3475</v>
+      </c>
+      <c r="C23" s="122">
+        <v>2670</v>
+      </c>
+      <c r="D23" s="123">
+        <v>805</v>
+      </c>
+      <c r="E23" s="166"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="86"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="87"/>
+      <c r="J23" s="87"/>
     </row>
     <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="93" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="121">
-        <v>1665</v>
-      </c>
-      <c r="C24" s="121">
-        <v>1280</v>
-      </c>
-      <c r="D24" s="122">
-        <v>385</v>
-      </c>
-      <c r="E24" s="85"/>
-      <c r="F24" s="138"/>
-      <c r="G24" s="87"/>
-      <c r="H24" s="87"/>
-      <c r="I24" s="88"/>
-      <c r="J24" s="88"/>
+        <v>67</v>
+      </c>
+      <c r="B24" s="122">
+        <v>3118</v>
+      </c>
+      <c r="C24" s="122">
+        <v>2414</v>
+      </c>
+      <c r="D24" s="123">
+        <v>704</v>
+      </c>
+      <c r="E24" s="166"/>
+      <c r="F24" s="157"/>
+      <c r="G24" s="86"/>
+      <c r="H24" s="86"/>
+      <c r="I24" s="87"/>
+      <c r="J24" s="87"/>
     </row>
     <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="93" t="s">
-        <v>70</v>
-      </c>
-      <c r="B25" s="121">
-        <v>1199</v>
-      </c>
-      <c r="C25" s="121">
-        <v>850</v>
-      </c>
-      <c r="D25" s="122">
-        <v>349</v>
-      </c>
-      <c r="E25" s="85"/>
-      <c r="F25" s="138"/>
-      <c r="G25" s="87"/>
-      <c r="H25" s="87"/>
-      <c r="I25" s="88"/>
-      <c r="J25" s="88"/>
+        <v>68</v>
+      </c>
+      <c r="B25" s="122">
+        <v>1846</v>
+      </c>
+      <c r="C25" s="122">
+        <v>1420</v>
+      </c>
+      <c r="D25" s="123">
+        <v>426</v>
+      </c>
+      <c r="E25" s="166"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="87"/>
+      <c r="J25" s="87"/>
     </row>
     <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="93" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" s="121">
-        <v>8326</v>
-      </c>
-      <c r="C26" s="121">
-        <v>5631</v>
-      </c>
-      <c r="D26" s="122">
-        <v>2695</v>
-      </c>
-      <c r="E26" s="85"/>
-      <c r="F26" s="138"/>
-      <c r="G26" s="87"/>
-      <c r="H26" s="87"/>
-      <c r="I26" s="88"/>
-      <c r="J26" s="88"/>
+        <v>69</v>
+      </c>
+      <c r="B26" s="122">
+        <v>1167</v>
+      </c>
+      <c r="C26" s="122">
+        <v>791</v>
+      </c>
+      <c r="D26" s="123">
+        <v>376</v>
+      </c>
+      <c r="E26" s="166"/>
+      <c r="F26" s="157"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="87"/>
+      <c r="J26" s="87"/>
     </row>
     <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="93" t="s">
-        <v>72</v>
-      </c>
-      <c r="B27" s="121">
-        <v>1637</v>
-      </c>
-      <c r="C27" s="121">
-        <v>1363</v>
-      </c>
-      <c r="D27" s="122">
-        <v>274</v>
-      </c>
-      <c r="E27" s="85"/>
-      <c r="F27" s="138"/>
+        <v>70</v>
+      </c>
+      <c r="B27" s="122">
+        <v>9698</v>
+      </c>
+      <c r="C27" s="122">
+        <v>6638</v>
+      </c>
+      <c r="D27" s="123">
+        <v>3060</v>
+      </c>
+      <c r="E27" s="166"/>
+      <c r="F27" s="157"/>
+      <c r="G27" s="86"/>
+      <c r="H27" s="86"/>
+      <c r="I27" s="87"/>
+      <c r="J27" s="87"/>
     </row>
     <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="93" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="121">
-        <v>1446</v>
-      </c>
-      <c r="C28" s="121">
-        <v>954</v>
-      </c>
-      <c r="D28" s="122">
-        <v>492</v>
-      </c>
-      <c r="E28" s="85"/>
-      <c r="F28" s="138"/>
+        <v>71</v>
+      </c>
+      <c r="B28" s="122">
+        <v>1834</v>
+      </c>
+      <c r="C28" s="122">
+        <v>1550</v>
+      </c>
+      <c r="D28" s="123">
+        <v>284</v>
+      </c>
+      <c r="E28" s="166"/>
+      <c r="F28" s="157"/>
     </row>
     <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="93" t="s">
-        <v>74</v>
-      </c>
-      <c r="B29" s="121">
-        <v>3348</v>
-      </c>
-      <c r="C29" s="121">
-        <v>2492</v>
-      </c>
-      <c r="D29" s="122">
-        <v>856</v>
-      </c>
-      <c r="E29" s="85"/>
-      <c r="F29" s="138"/>
-      <c r="G29" s="87"/>
-      <c r="H29" s="87"/>
+        <v>72</v>
+      </c>
+      <c r="B29" s="122">
+        <v>1357</v>
+      </c>
+      <c r="C29" s="122">
+        <v>914</v>
+      </c>
+      <c r="D29" s="123">
+        <v>443</v>
+      </c>
+      <c r="E29" s="166"/>
+      <c r="F29" s="157"/>
     </row>
     <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="93" t="s">
-        <v>75</v>
-      </c>
-      <c r="B30" s="121">
-        <v>72</v>
-      </c>
-      <c r="C30" s="121">
-        <v>55</v>
-      </c>
-      <c r="D30" s="122">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="89" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="122">
+        <v>3459</v>
+      </c>
+      <c r="C30" s="122">
+        <v>2558</v>
+      </c>
+      <c r="D30" s="123">
+        <v>901</v>
+      </c>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="86"/>
+      <c r="H30" s="86"/>
+    </row>
+    <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="93" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="122">
         <v>78</v>
+      </c>
+      <c r="C31" s="122">
+        <v>50</v>
+      </c>
+      <c r="D31" s="123">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="88" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
